--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -492,8 +492,8 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,7 +512,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>solved</t>
+          <t>infeasible</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7.43844</v>
+        <v>30287.1</v>
       </c>
     </row>
     <row r="5">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1e-06</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="6">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>626.71300112923</v>
+        <v>41.1256</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.0010217484571</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="8">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -573,17 +573,17 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>0</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Q Balance Error (MVAr)</t>
+          <t>Net Grid Q Losses (MVAr)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>626.7119793807728</v>
+        <v>605.6243999999999</v>
       </c>
     </row>
     <row r="11">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.186894349531278</v>
+        <v>4.841792614624468</v>
       </c>
     </row>
     <row r="12">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.8460276516565021</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -660,28 +660,28 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>0.0 injecting: stationarity violated. lam_inj=0.9040, expected=0.0000</t>
+          <t>0 injecting: stationarity violated. lam_inj=5.0000, expected=0.9410</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>1.0 injecting: stationarity violated. lam_inj=1.4085, expected=0.0000</t>
+          <t>1 injecting: stationarity violated. lam_inj=5.0000, expected=1.4360</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>2.0 injecting: stationarity violated. lam_inj=1.2057, expected=0.0000</t>
+          <t>2 injecting: stationarity violated. lam_inj=4.3877, expected=1.2319</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>3.0 absorbing: stationarity violated. lam_abs=0.8500, expected=-0.0000</t>
+          <t>3 absorbing: stationarity violated. lam_abs=5.0000, expected=0.8915</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
@@ -791,19 +791,19 @@
         <v>11</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.903967</v>
+        <v>5</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>0.730571</v>
+        <v>0</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>198.368</v>
+        <v>20.5</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>1.11853e-08</v>
+        <v>0</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>198.368</v>
+        <v>20.5</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
@@ -811,13 +811,13 @@
         </is>
       </c>
       <c r="J2" s="10" t="n">
-        <v>179.3181258641717</v>
+        <v>102.5</v>
       </c>
       <c r="K2" s="10" t="n">
-        <v>187.3141958641717</v>
+        <v>26.8702</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>-7.99607</v>
+        <v>75.6298</v>
       </c>
     </row>
     <row r="3">
@@ -835,19 +835,19 @@
         <v>12</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1.40853</v>
+        <v>5</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>7.42463e-07</v>
+        <v>0</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>236.951</v>
+        <v>10</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>4.7759e-06</v>
+        <v>0</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>236.951</v>
+        <v>10</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="J3" s="10" t="n">
-        <v>333.7525920300035</v>
+        <v>50</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>339.7424820300035</v>
+        <v>20.18</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>-5.98989</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="4">
@@ -879,19 +879,19 @@
         <v>13</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>1.20574</v>
+        <v>4.38767</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>1.03524</v>
+        <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>191.394</v>
+        <v>10.6256</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1.13718e-08</v>
+        <v>0</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>191.394</v>
+        <v>10.6256</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="J4" s="10" t="n">
-        <v>230.7714015717726</v>
+        <v>46.621626352</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>237.7659115717726</v>
+        <v>19.920226352</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>-6.99451</v>
+        <v>26.7014</v>
       </c>
     </row>
     <row r="5">
@@ -923,19 +923,19 @@
         <v>10</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.329492</v>
+        <v>0</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.85</v>
+        <v>5</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1.12923e-06</v>
+        <v>0</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0.00101695</v>
+        <v>20.75</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>-0.00101582</v>
+        <v>-20.75</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.00086477957225116</v>
+        <v>103.75</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>6.000864779572251</v>
+        <v>24.0681</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>-6</v>
+        <v>79.6819</v>
       </c>
     </row>
   </sheetData>
@@ -1028,13 +1028,13 @@
         <v>0.9</v>
       </c>
       <c r="D2" s="15" t="n">
-        <v>1.03215</v>
+        <v>1.03556</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>-3.69838</v>
+        <v>-1.39466</v>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
@@ -1057,13 +1057,13 @@
         <v>0.9</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>1.00434</v>
+        <v>0.95</v>
       </c>
       <c r="E3" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-1.9971</v>
+        <v>2.6476</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -1086,13 +1086,13 @@
         <v>0.9</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.984239</v>
+        <v>0.987775</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>-34.3591</v>
+        <v>-23.5201</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         <v>0.9</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.950001</v>
+        <v>0.95</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>-39.4882</v>
+        <v>-26.4471</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -1144,13 +1144,13 @@
         <v>0.9</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>0.964878</v>
+        <v>0.958525</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>-29.1253</v>
+        <v>-20.9333</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -1173,13 +1173,13 @@
         <v>0.9</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>1.00518</v>
+        <v>1.04997</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-32.0298</v>
+        <v>-1.83619</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         <v>0.9</v>
       </c>
       <c r="D8" s="15" t="n">
-        <v>1.00536</v>
+        <v>1.05</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-32.017</v>
+        <v>-1.8233</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1231,13 +1231,13 @@
         <v>0.9</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>1.04234</v>
+        <v>1.05</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-6.15048</v>
+        <v>-3.19175</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1260,13 +1260,13 @@
         <v>0.9</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.993431</v>
+        <v>1.00346</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>-31.787</v>
+        <v>-21.6151</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>0.9</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>1.03</v>
+        <v>1.03264</v>
       </c>
       <c r="E11" s="15" t="n">
         <v>1.1</v>
@@ -1318,13 +1318,13 @@
         <v>0.9</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>1.02744</v>
+        <v>0.952461</v>
       </c>
       <c r="E12" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>1.6144</v>
+        <v>6.76705</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0.9</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>1.01427</v>
+        <v>0.98874</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-32.8667</v>
+        <v>-21.9946</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>1.1</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>-27.7796</v>
+        <v>2.23367</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="D2" s="11" t="n">
-        <v>30.7781</v>
+        <v>-64.4335</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>-40.5175</v>
+        <v>121.29</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>50.88181645597963</v>
+        <v>137.342418874323</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>434.4009395973707</v>
+        <v>434.4010844790632</v>
       </c>
       <c r="H2" s="17" t="n">
-        <v>0.117131</v>
+        <v>0.316165</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>-204.205</v>
+        <v>2.34285</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>-28.1544</v>
+        <v>-6.4219</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>206.1367319629377</v>
+        <v>6.835915866400053</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>434.4000656708877</v>
+        <v>434.3987459981605</v>
       </c>
       <c r="H3" s="17" t="n">
-        <v>0.474532</v>
+        <v>0.0157365</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -1554,19 +1554,19 @@
         </is>
       </c>
       <c r="D4" s="11" t="n">
-        <v>-183.894</v>
+        <v>148.193</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>-29.1067</v>
+        <v>3.22588</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>186.1832517196163</v>
+        <v>148.2281064804324</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>434.399640968869</v>
+        <v>434.3986287106857</v>
       </c>
       <c r="H4" s="17" t="n">
-        <v>0.428599</v>
+        <v>0.341226</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="D5" s="11" t="n">
-        <v>-212.53</v>
+        <v>128.462</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>-56.1961</v>
+        <v>72.6529</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>219.8340341148522</v>
+        <v>147.5836350087976</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>868.7993380870886</v>
+        <v>868.8034085406347</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.253032</v>
+        <v>0.16987</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -1628,19 +1628,19 @@
         </is>
       </c>
       <c r="D6" s="11" t="n">
-        <v>65.0335</v>
+        <v>-34.7891</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>-11.002</v>
+        <v>4.13285</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>65.95756307088672</v>
+        <v>35.03372557882618</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>434.4000307627093</v>
+        <v>434.4002130086261</v>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.151836</v>
+        <v>0.0806485</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="D7" s="11" t="n">
-        <v>51.8017</v>
+        <v>-164.255</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9.47611</v>
+        <v>25.1828</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>52.66130252492906</v>
+        <v>166.1742412073544</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>434.3988395826794</v>
+        <v>434.3993046634698</v>
       </c>
       <c r="H7" s="17" t="n">
-        <v>0.121228</v>
+        <v>0.382538</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="D8" s="11" t="n">
-        <v>-354.074</v>
+        <v>262.298</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-80.73439999999999</v>
+        <v>51.7716</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>363.1617281864376</v>
+        <v>267.3584473521643</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>868.7996482962785</v>
+        <v>868.8000550872487</v>
       </c>
       <c r="H8" s="17" t="n">
-        <v>0.418004</v>
+        <v>0.307733</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="D9" s="11" t="n">
-        <v>299.985</v>
+        <v>-299.989</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>161.443</v>
+        <v>10.6852</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>340.6682293287708</v>
+        <v>300.1792358242654</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>434.4005800990669</v>
+        <v>434.4002139218335</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>0.784226</v>
+        <v>0.6910200000000001</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="D10" s="11" t="n">
-        <v>-354.074</v>
+        <v>262.298</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>73.35299999999999</v>
+        <v>-110.946</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>361.5923949490642</v>
+        <v>284.7968674687276</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>1000.001092250559</v>
+        <v>999.9995346465292</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>0.361592</v>
+        <v>0.284797</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -1813,19 +1813,19 @@
         </is>
       </c>
       <c r="D11" s="11" t="n">
-        <v>337.53</v>
+        <v>-253.462</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>62.0197</v>
+        <v>-114.992</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>343.1806289522909</v>
+        <v>278.327407037108</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>999.9989187987998</v>
+        <v>1000.001462442048</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>0.343181</v>
+        <v>0.278327</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -1850,19 +1850,19 @@
         </is>
       </c>
       <c r="D12" s="11" t="n">
-        <v>527.501</v>
+        <v>-200.207</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>-34.098</v>
+        <v>25.6891</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>528.6019093845575</v>
+        <v>201.848390401831</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>999.9998285752939</v>
+        <v>999.996979929705</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>0.528602</v>
+        <v>0.201849</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="D13" s="11" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>-3.6264e-08</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>162.735</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>525.8162038440809</v>
-      </c>
       <c r="G13" s="11" t="n">
-        <v>1000.000387671887</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>0.5258160000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1924,19 +1924,19 @@
         </is>
       </c>
       <c r="D14" s="11" t="n">
-        <v>200</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>224.802</v>
+        <v>-4.66759</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>300.8919061789466</v>
+        <v>200.0544585766788</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>999.9996881902697</v>
+        <v>1000.002292264483</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>0.300892</v>
+        <v>0.200054</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1961,19 +1961,19 @@
         </is>
       </c>
       <c r="D15" s="11" t="n">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>161.531</v>
+        <v>10.6256</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>340.7231485546587</v>
+        <v>300.1881133145681</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>500.0002179991645</v>
+        <v>500.0001887393369</v>
       </c>
       <c r="H15" s="17" t="n">
-        <v>0.681446</v>
+        <v>0.600376</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1997,17 +1997,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -2085,37 +2085,37 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>2.27032e-10</v>
+        <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>2.18054e-10</v>
+        <v>0</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>2.22366e-10</v>
+        <v>0</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>0.419429</v>
+        <v>0.009999020000000001</v>
       </c>
       <c r="F2" s="19" t="n">
-        <v>0.903966999991022</v>
+        <v>5</v>
       </c>
       <c r="G2" s="19" t="n">
-        <v>1.149999999777634</v>
+        <v>0.009999020000000001</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>4.5035883776e-10</v>
+        <v>0</v>
       </c>
       <c r="I2" s="15" t="n">
-        <v>4.3254935872e-10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="15" t="n">
-        <v>2.4872304198e-20</v>
+        <v>0</v>
       </c>
       <c r="K2" s="15" t="n">
-        <v>4.6914391937e-11</v>
+        <v>0</v>
       </c>
       <c r="L2" s="15" t="n">
-        <v>2.2188055904e-10</v>
+        <v>0</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -2130,37 +2130,37 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>2.31057e-10</v>
+        <v>0</v>
       </c>
       <c r="C3" s="18" t="n">
-        <v>2.16809e-10</v>
+        <v>0</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>2.22441e-10</v>
+        <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>1.75</v>
+        <v>0.00999826</v>
       </c>
       <c r="F3" s="19" t="n">
-        <v>1.408529999985752</v>
+        <v>5</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>1.750000742240559</v>
+        <v>0.00999826</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>5.4749187207e-10</v>
+        <v>0</v>
       </c>
       <c r="I3" s="15" t="n">
-        <v>5.1373109359e-10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="15" t="n">
-        <v>1.0623559719e-17</v>
+        <v>0</v>
       </c>
       <c r="K3" s="15" t="n">
-        <v>8.357825e-08</v>
+        <v>0</v>
       </c>
       <c r="L3" s="15" t="n">
-        <v>1.1316542809e-07</v>
+        <v>0</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -2175,37 +2175,37 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>2.28145e-10</v>
+        <v>0</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>2.18319e-10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>2.22495e-10</v>
+        <v>0</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.464761</v>
+        <v>0.0065398</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>1.205739999990174</v>
+        <v>4.38767</v>
       </c>
       <c r="G4" s="19" t="n">
-        <v>1.500000999777505</v>
+        <v>0.0065398</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>4.366558413e-10</v>
+        <v>0</v>
       </c>
       <c r="I4" s="15" t="n">
-        <v>4.1784946686e-10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="15" t="n">
-        <v>2.530168641e-20</v>
+        <v>0</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>5.2851691398e-11</v>
+        <v>0</v>
       </c>
       <c r="L4" s="15" t="n">
-        <v>2.1764942892e-10</v>
+        <v>0</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -2220,37 +2220,37 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>2.22269e-10</v>
+        <v>0</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>0.370508</v>
+        <v>0.00996414</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>2.2231e-10</v>
+        <v>0</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>2.24851e-08</v>
+        <v>0</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.6999999997777311</v>
+        <v>0.00996414</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.85000002226279</v>
+        <v>5</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>2.5099282287e-18</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>4.1838874884e-09</v>
+        <v>0</v>
       </c>
       <c r="J5" s="15" t="n">
-        <v>2.260781545e-15</v>
+        <v>0</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>2.2866222445e-13</v>
+        <v>0</v>
       </c>
       <c r="L5" s="15" t="n">
-        <v>1.1483704485e-13</v>
+        <v>0</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>626.71300112923</v>
+        <v>41.1256</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0010217484571</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="5">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6">
@@ -2326,17 +2326,17 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>q_balance_error_mvar</t>
+          <t>net_grid_q_losses_mvar</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>626.7119793807728</v>
+        <v>605.6243999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>7.43844</v>
+        <v>30287.1</v>
       </c>
     </row>
     <row r="9">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.186894349531278</v>
+        <v>4.841792614624468</v>
       </c>
     </row>
     <row r="10">
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.8460276516565021</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (78.4%)</t>
+          <t>6.0-&gt;7.0 (69.1%)</t>
         </is>
       </c>
     </row>
@@ -2475,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.903967</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.730571</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.40853</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7.42463e-07</v>
+        <v>0</v>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.20574</v>
+        <v>4.38767</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.03524</v>
+        <v>0</v>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
@@ -2547,10 +2547,10 @@
         <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.329492</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.85</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30287.1</v>
+        <v>302.874</v>
       </c>
     </row>
     <row r="5">
@@ -1890,7 +1890,7 @@
         <v>-500</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>-3.6264e-08</v>
+        <v>-3.62642e-08</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>500</v>
@@ -2139,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0.00999826</v>
+        <v>0.00999829</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>5</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>0.00999826</v>
+        <v>0.00999829</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>0</v>
@@ -2184,13 +2184,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.0065398</v>
+        <v>0.00648579</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4.38767</v>
       </c>
       <c r="G4" s="19" t="n">
-        <v>0.0065398</v>
+        <v>0.00648579</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>0.00996414</v>
+        <v>0.00996415</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.00996414</v>
+        <v>0.00996415</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>5</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>30287.1</v>
+        <v>302.874</v>
       </c>
     </row>
     <row r="9">

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -1179,7 +1179,7 @@
         <v>1.1</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-1.83619</v>
+        <v>-1.8362</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="D3" s="11" t="n">
-        <v>2.34285</v>
+        <v>2.34286</v>
       </c>
       <c r="E3" s="11" t="n">
         <v>-6.4219</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>6.835915866400053</v>
+        <v>6.835919293672212</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>434.3987459981605</v>
+        <v>434.3989637894203</v>
       </c>
       <c r="H3" s="17" t="n">
         <v>0.0157365</v>
@@ -1890,7 +1890,7 @@
         <v>-500</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>-3.62642e-08</v>
+        <v>-3.62596e-08</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>500</v>
@@ -1998,9 +1998,9 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
@@ -2094,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>0.009999020000000001</v>
+        <v>80.37130000000001</v>
       </c>
       <c r="F2" s="19" t="n">
         <v>5</v>
       </c>
       <c r="G2" s="19" t="n">
-        <v>0.009999020000000001</v>
+        <v>80.37130000000001</v>
       </c>
       <c r="H2" s="15" t="n">
         <v>0</v>
@@ -2139,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0.00999829</v>
+        <v>109.337</v>
       </c>
       <c r="F3" s="19" t="n">
         <v>5</v>
       </c>
       <c r="G3" s="19" t="n">
-        <v>0.00999829</v>
+        <v>109.337</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>0</v>
@@ -2184,13 +2184,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>0.00648579</v>
+        <v>101.445</v>
       </c>
       <c r="F4" s="19" t="n">
         <v>4.38767</v>
       </c>
       <c r="G4" s="19" t="n">
-        <v>0.00648579</v>
+        <v>101.445</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>0.00996415</v>
+        <v>2.93639</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.00996415</v>
+        <v>2.93639</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>5</v>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,9 +48,6 @@
       <sz val="12"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -65,8 +62,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,21 +105,20 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,11 +485,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="69" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infeasible</t>
+          <t>solved</t>
         </is>
       </c>
     </row>
@@ -523,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>302.874</v>
+        <v>1128.7</v>
       </c>
     </row>
     <row r="5">
@@ -543,7 +539,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>41.1256</v>
+        <v>618.3480000000001</v>
       </c>
     </row>
     <row r="7">
@@ -553,7 +549,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -583,7 +579,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>605.6243999999999</v>
+        <v>7.652000000000044</v>
       </c>
     </row>
     <row r="11">
@@ -593,7 +589,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.841792614624468</v>
+        <v>1.825353265911752</v>
       </c>
     </row>
     <row r="12">
@@ -603,7 +599,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +619,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -633,7 +629,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16"/>
@@ -653,35 +649,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>0 injecting: stationarity violated. lam_inj=5.0000, expected=0.9410</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>1 injecting: stationarity violated. lam_inj=5.0000, expected=1.4360</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>2 injecting: stationarity violated. lam_inj=4.3877, expected=1.2319</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>3 absorbing: stationarity violated. lam_abs=5.0000, expected=0.8915</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -708,248 +676,248 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>λ_inj (€/MVAr)</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>λ_abs (€/MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Q_inj (MVAr)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Q_abs (MVAr)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Q_net (MVAr)</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>revenue (€)</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>cost (€)</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>profit (€)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="D2" s="8" t="n">
+        <v>1.26933</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>184.667</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>184.667</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J2" s="10" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>26.8702</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>75.6298</v>
+      <c r="J2" s="8" t="n">
+        <v>234.40336311</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>208.30146311</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>26.1019</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11" t="n">
+      <c r="D3" s="8" t="n">
+        <v>2.29046</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>247.351</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>247.351</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>566.54757146</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>462.41957146</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>104.128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1.75899</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>186.33</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>186.33</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>327.7526067000001</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>282.6744067000001</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>45.0782</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>29.82</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>4.38767</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>10.6256</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>10.6256</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>46.621626352</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>19.920226352</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>26.7014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>-20.75</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>ABSORPTION</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>103.75</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>24.0681</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>79.6819</v>
+      <c r="D5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>3.94217e-15</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>9.206949999999999e-15</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>-9.206949999999999e-15</v>
       </c>
     </row>
   </sheetData>
@@ -977,414 +945,414 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>V_min</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>V_pu</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>V_max</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>θ (deg)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D2" s="15" t="n">
-        <v>1.03556</v>
-      </c>
-      <c r="E2" s="15" t="n">
+      <c r="D2" s="13" t="n">
+        <v>1.03215</v>
+      </c>
+      <c r="E2" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>-1.39466</v>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="F2" s="14" t="n">
+        <v>-3.69614</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D3" s="15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E3" s="15" t="n">
+      <c r="D3" s="13" t="n">
+        <v>0.995985</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F3" s="16" t="n">
-        <v>2.6476</v>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="F3" s="14" t="n">
+        <v>-1.84716</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D4" s="15" t="n">
-        <v>0.987775</v>
-      </c>
-      <c r="E4" s="15" t="n">
+      <c r="D4" s="13" t="n">
+        <v>0.998326</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <v>-23.5201</v>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="14" t="n">
+        <v>-34.1476</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E5" s="15" t="n">
+      <c r="D5" s="13" t="n">
+        <v>0.961989</v>
+      </c>
+      <c r="E5" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>-26.4471</v>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="F5" s="14" t="n">
+        <v>-39.1664</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>0.958525</v>
-      </c>
-      <c r="E6" s="15" t="n">
+      <c r="D6" s="13" t="n">
+        <v>0.967239</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>-20.9333</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="F6" s="14" t="n">
+        <v>-29.0536</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D7" s="15" t="n">
-        <v>1.04997</v>
-      </c>
-      <c r="E7" s="15" t="n">
+      <c r="D7" s="13" t="n">
+        <v>1.00644</v>
+      </c>
+      <c r="E7" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>-1.8362</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="F7" s="14" t="n">
+        <v>-31.842</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="13" t="n">
+        <v>1.00661</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>-31.8292</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1.04358</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>-6.15869</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>1.00676</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>-31.6307</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1.01753</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1.83019</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1.02925</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>-32.6977</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E14" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <v>-1.8233</v>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>-3.19175</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>1.00346</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>-21.6151</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>1.03264</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0.952461</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>6.76705</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>0.98874</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-21.9946</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>2.23367</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="F14" s="14" t="n">
+        <v>-27.5971</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1412,570 +1380,570 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>from_bus</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>to_bus</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>P_flow (MW)</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Q_flow (MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>|S_flow| (MVA)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>S_max (MVA)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>loading (%)</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
-        <v>-64.4335</v>
-      </c>
-      <c r="E2" s="11" t="n">
-        <v>121.29</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>137.342418874323</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>434.4010844790632</v>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>0.316165</v>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="D2" s="9" t="n">
+        <v>31.9228</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>-51.2774</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>60.40229226279413</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>434.3988569615826</v>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>0.139048</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>2.34286</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>-6.4219</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>6.835919293672212</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>434.3989637894203</v>
-      </c>
-      <c r="H3" s="17" t="n">
-        <v>0.0157365</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="D3" s="9" t="n">
+        <v>-203.1</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>-27.2272</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>204.9168866146468</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>434.3990388778351</v>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>0.471725</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>148.193</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>3.22588</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>148.2281064804324</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>434.3986287106857</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.341226</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="D4" s="9" t="n">
+        <v>-182.615</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-24.8479</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>184.2977383458896</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>434.3991249352156</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>0.424259</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>128.462</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>72.6529</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>147.5836350087976</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>868.8034085406347</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>0.16987</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="D5" s="9" t="n">
+        <v>-214.512</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>-61.9892</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>223.2891825876032</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>868.7990793614356</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.257009</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>-34.7891</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>4.13285</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>35.03372557882618</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>434.4002130086261</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>0.0806485</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="D6" s="9" t="n">
+        <v>63.8822</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-14.294</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>65.46185082045878</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>434.3996205611253</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.150695</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>-164.255</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>25.1828</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>166.1742412073544</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>434.3993046634698</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0.382538</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="D7" s="9" t="n">
+        <v>50.98</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>5.76608</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>51.30504925020927</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>434.3983307385677</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.118106</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>262.298</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>51.7716</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>267.3584473521643</v>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>868.8000550872487</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>0.307733</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="D8" s="9" t="n">
+        <v>-356.004</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-70.9945</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>363.0138661900534</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>868.8013301727088</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0.417833</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>-299.989</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>10.6852</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>300.1792358242654</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>434.4002139218335</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0.6910200000000001</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="D9" s="9" t="n">
+        <v>299.985</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>156.832</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>338.5074245108961</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>434.4004564773604</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.7792520000000001</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>262.298</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>-110.946</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>284.7968674687276</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>999.9995346465292</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.284797</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="D10" s="9" t="n">
+        <v>-356.004</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>83.1435</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>365.5840390501889</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1000.000106815914</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>0.365584</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>-253.462</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>-114.992</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>278.327407037108</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>1000.001462442048</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>0.278327</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="D11" s="9" t="n">
+        <v>339.512</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>57.2949</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>344.3125087910836</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>999.9985733651753</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0.344313</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>-200.207</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>25.6891</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>201.848390401831</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>999.996979929705</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0.201849</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="D12" s="9" t="n">
+        <v>527.181</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>-34.0556</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>528.2798412322393</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>999.9996994628591</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0.5282800000000001</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>-500</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>-3.62596e-08</v>
-      </c>
-      <c r="F13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="E13" s="9" t="n">
+        <v>148.995</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>521.727428860128</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1000.000822001024</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0.5217269999999999</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>-200</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>-4.66759</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>200.0544585766788</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>1000.002292264483</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>0.200054</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="D14" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>234.934</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>308.5352238497251</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1000.000725524576</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>0.308535</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>-300</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>10.6256</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>300.1881133145681</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>500.0001887393369</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0.600376</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="D15" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>156.918</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>338.5605687672444</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>500.0001015582803</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>0.6771210000000001</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1997,13 +1965,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
@@ -2012,67 +1980,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>μ_qp_ub</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>μ_qp_lb</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>μ_qn_ub</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>μ_qn_lb</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>stat_inj_residual</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>stat_abs_residual</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>compl_qp_ub_violation</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>compl_qp_lb_violation</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>compl_qn_ub_violation</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>compl_qn_lb_violation</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>exclusivity_violation</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>overall_status</t>
         </is>
@@ -2084,40 +2052,40 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="18" t="n">
-        <v>80.37130000000001</v>
-      </c>
-      <c r="F2" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="19" t="n">
-        <v>80.37130000000001</v>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="B2" s="16" t="n">
+        <v>1.69625e-16</v>
+      </c>
+      <c r="C2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>3.9846e-17</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1.26933</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>3.1324139875e-16</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2129,40 +2097,40 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="18" t="n">
-        <v>109.337</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>109.337</v>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="B3" s="16" t="n">
+        <v>1.87274e-15</v>
+      </c>
+      <c r="C3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>2.290459999999998</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>4.632241117400001e-15</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2174,40 +2142,40 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>101.445</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>4.38767</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>101.445</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="B4" s="16" t="n">
+        <v>9.01764e-17</v>
+      </c>
+      <c r="C4" s="16" t="n">
+        <v>2.05962e-40</v>
+      </c>
+      <c r="D4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>1.75899</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>1.6802568612e-16</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>3.837689946000001e-40</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2219,40 +2187,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>2.93639</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>2.93639</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="B5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>2.15793e-16</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>0.8499999999999998</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2296,7 +2264,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>41.1256</v>
+        <v>618.3480000000001</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2274,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>20.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2336,7 +2304,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>605.6243999999999</v>
+        <v>7.652000000000044</v>
       </c>
     </row>
     <row r="8">
@@ -2346,7 +2314,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>302.874</v>
+        <v>1128.7</v>
       </c>
     </row>
     <row r="9">
@@ -2356,7 +2324,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>4.841792614624468</v>
+        <v>1.825353265911752</v>
       </c>
     </row>
     <row r="10">
@@ -2366,7 +2334,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2386,7 +2354,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2396,7 +2364,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2405,7 +2373,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="16" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2417,7 +2385,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (69.1%)</t>
+          <t>6.0-&gt;7.0 (77.9%)</t>
         </is>
       </c>
     </row>
@@ -2431,32 +2399,32 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>injection_deadband_price (€/MVAr)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>absorption_deadband_price (€/MVAr)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>actual_lam_inj (€/MVAr)</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>actual_lam_abs (€/MVAr)</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>in_deadband?</t>
         </is>
@@ -2475,12 +2443,12 @@
         <v>0</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5</v>
+        <v>1.26933</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2499,12 +2467,12 @@
         <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>5</v>
+        <v>2.29046</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2523,12 +2491,12 @@
         <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4.38767</v>
+        <v>1.75899</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2550,11 +2518,11 @@
         <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,12 +78,6 @@
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -97,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,8 +111,6 @@
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -984,22 +976,22 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>1.03215</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F2" s="14" t="n">
         <v>-3.69614</v>
@@ -1013,22 +1005,22 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>0.995985</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F3" s="14" t="n">
         <v>-1.84716</v>
@@ -1042,22 +1034,22 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0.998326</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F4" s="14" t="n">
         <v>-34.1476</v>
@@ -1071,22 +1063,22 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>0.961989</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>-39.1664</v>
@@ -1100,22 +1092,22 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>0.967239</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F6" s="14" t="n">
         <v>-29.0536</v>
@@ -1129,22 +1121,22 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>1.00644</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F7" s="14" t="n">
         <v>-31.842</v>
@@ -1158,22 +1150,22 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>1.00661</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>-31.8292</v>
@@ -1187,22 +1179,22 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>1.04358</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>-6.15869</v>
@@ -1216,22 +1208,22 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>1.00676</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>-31.6307</v>
@@ -1245,22 +1237,22 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>1.03</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>0</v>
@@ -1274,22 +1266,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>1.01753</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F12" s="14" t="n">
         <v>1.83019</v>
@@ -1303,22 +1295,22 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>1.02925</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F13" s="14" t="n">
         <v>-32.6977</v>
@@ -1332,22 +1324,22 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>1.05</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="F14" s="14" t="n">
         <v>-27.5971</v>
@@ -1969,8 +1961,8 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2064,20 +2056,20 @@
       <c r="E2" s="16" t="n">
         <v>1.15</v>
       </c>
-      <c r="F2" s="17" t="n">
-        <v>1.26933</v>
-      </c>
-      <c r="G2" s="17" t="n">
-        <v>1.15</v>
+      <c r="F2" s="13" t="n">
+        <v>4.000000000173625e-06</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>3.1324139875e-16</v>
+        <v>2.9740860125e-14</v>
       </c>
       <c r="I2" s="13" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="13" t="n">
-        <v>0</v>
+        <v>9.961500000000001e-15</v>
       </c>
       <c r="K2" s="13" t="n">
         <v>0</v>
@@ -2085,9 +2077,9 @@
       <c r="L2" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2109,14 +2101,14 @@
       <c r="E3" s="16" t="n">
         <v>1.75</v>
       </c>
-      <c r="F3" s="17" t="n">
-        <v>2.290459999999998</v>
-      </c>
-      <c r="G3" s="17" t="n">
-        <v>1.75</v>
+      <c r="F3" s="13" t="n">
+        <v>3.600000001754216e-06</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>4.632241117400001e-15</v>
+        <v>4.960888260000002e-15</v>
       </c>
       <c r="I3" s="13" t="n">
         <v>0</v>
@@ -2130,9 +2122,9 @@
       <c r="L3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M3" s="18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2154,17 +2146,17 @@
       <c r="E4" s="16" t="n">
         <v>1.5</v>
       </c>
-      <c r="F4" s="17" t="n">
-        <v>1.75899</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>1.5</v>
+      <c r="F4" s="13" t="n">
+        <v>9.01764e-17</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>1.6802568612e-16</v>
+        <v>3.036239388000001e-15</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>3.837689946000001e-40</v>
+        <v>3.837689946000001e-38</v>
       </c>
       <c r="J4" s="13" t="n">
         <v>0</v>
@@ -2175,9 +2167,9 @@
       <c r="L4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2199,11 +2191,11 @@
       <c r="E5" s="16" t="n">
         <v>0.85</v>
       </c>
-      <c r="F5" s="17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>0.8499999999999998</v>
+      <c r="F5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>0</v>
@@ -2212,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0</v>
+        <v>7.552755000000001e-14</v>
       </c>
       <c r="K5" s="13" t="n">
         <v>0</v>
@@ -2220,9 +2212,9 @@
       <c r="L5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2433,14 +2425,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1.26933</v>
@@ -2457,14 +2449,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>2.29046</v>
@@ -2481,14 +2473,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1.75899</v>
@@ -2505,14 +2497,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>0</v>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -72,12 +72,6 @@
         <bgColor rgb="00002060"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,9 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -477,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -511,7 +502,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1128.7</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="5">
@@ -527,119 +518,129 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Total Q Injected (MVAr)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>618.3480000000001</v>
+          <t>Reference Bus P_ref (MW)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>27.2531167015847</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Total Q Absorbed (MVAr)</t>
+          <t>Total Q Injected (MVAr)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Total Q Shunt (MVAr)</t>
+          <t>Total Q Absorbed (MVAr)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Total Q Load (MVAr)</t>
+          <t>Total Q Shunt (MVAr)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1046</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Net Grid Q Losses (MVAr)</t>
+          <t>Total Q Load (MVAr)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>7.652000000000044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Avg Injection Price (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>1.825353265911752</v>
+          <t>Net Grid Q Losses (MVAr)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Avg Absorption Price (€/MVAr)</t>
+          <t>Avg Injection Price (€/MVAr)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Generators Injecting</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
+          <t>Avg Absorption Price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Generators Absorbing</t>
+          <t>Generators Injecting</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Generators Absorbing</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Generators Idle</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="17"/>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Consistency Checks</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Dual Price Consistency</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -671,7 +672,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -748,22 +749,22 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="8" t="n">
-        <v>1.26933</v>
+        <v>0.719973</v>
       </c>
       <c r="E2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>184.667</v>
+        <v>12.4832</v>
       </c>
       <c r="G2" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>184.667</v>
+        <v>12.4832</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -771,13 +772,13 @@
         </is>
       </c>
       <c r="J2" s="8" t="n">
-        <v>234.40336311</v>
+        <v>8.9875669536</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>208.30146311</v>
+        <v>13.8629069536</v>
       </c>
       <c r="L2" s="8" t="n">
-        <v>26.1019</v>
+        <v>-4.87534</v>
       </c>
     </row>
     <row r="3">
@@ -792,22 +793,22 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>2.29046</v>
+        <v>1.26786</v>
       </c>
       <c r="E3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>247.351</v>
+        <v>183.931</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>247.351</v>
+        <v>183.931</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -815,13 +816,13 @@
         </is>
       </c>
       <c r="J3" s="8" t="n">
-        <v>566.54757146</v>
+        <v>233.19875766</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>462.41957146</v>
+        <v>207.36825766</v>
       </c>
       <c r="L3" s="8" t="n">
-        <v>104.128</v>
+        <v>25.8305</v>
       </c>
     </row>
     <row r="4">
@@ -836,80 +837,80 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>2.23035</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>514.4346882</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>424.6742882</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>89.7604</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>1.75899</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>186.33</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>186.33</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="D5" s="8" t="n">
+        <v>1.76311</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="8" t="n">
-        <v>327.7526067000001</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>282.6744067000001</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>45.0782</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>3.94217e-15</v>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>9.206949999999999e-15</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>-9.206949999999999e-15</v>
+      <c r="J5" s="8" t="n">
+        <v>330.93927322</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>285.09097322</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>45.8483</v>
       </c>
     </row>
   </sheetData>
@@ -984,17 +985,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>1.03215</v>
-      </c>
-      <c r="E2" s="13" t="n">
+      <c r="D2" s="10" t="n">
+        <v>1.04008</v>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>-3.69614</v>
+      <c r="F2" s="11" t="n">
+        <v>2.23655</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -1013,17 +1014,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>0.995985</v>
-      </c>
-      <c r="E3" s="13" t="n">
+      <c r="D3" s="10" t="n">
+        <v>1.00143</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>-1.84716</v>
+      <c r="F3" s="11" t="n">
+        <v>4.08351</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -1042,17 +1043,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>0.998326</v>
-      </c>
-      <c r="E4" s="13" t="n">
+      <c r="D4" s="10" t="n">
+        <v>0.984186</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>-34.1476</v>
+      <c r="F4" s="11" t="n">
+        <v>-28.0312</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -1071,17 +1072,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>0.961989</v>
-      </c>
-      <c r="E5" s="13" t="n">
+      <c r="D5" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>-39.1664</v>
+      <c r="F5" s="11" t="n">
+        <v>-33.1882</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -1100,17 +1101,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>0.967239</v>
-      </c>
-      <c r="E6" s="13" t="n">
+      <c r="D6" s="10" t="n">
+        <v>0.964028</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>-29.0536</v>
+      <c r="F6" s="11" t="n">
+        <v>-22.9809</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -1129,17 +1130,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>1.00644</v>
-      </c>
-      <c r="E7" s="13" t="n">
+      <c r="D7" s="10" t="n">
+        <v>1.0061</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>-31.842</v>
+      <c r="F7" s="11" t="n">
+        <v>-25.7428</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1158,17 +1159,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>1.00661</v>
-      </c>
-      <c r="E8" s="13" t="n">
+      <c r="D8" s="10" t="n">
+        <v>1.00627</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>-31.8292</v>
+      <c r="F8" s="11" t="n">
+        <v>-25.73</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -1187,17 +1188,17 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>1.04358</v>
-      </c>
-      <c r="E9" s="13" t="n">
+      <c r="D9" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>-6.15869</v>
+      <c r="E9" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
@@ -1216,17 +1217,17 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>1.00676</v>
-      </c>
-      <c r="E10" s="13" t="n">
+      <c r="D10" s="10" t="n">
+        <v>0.994143</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>-31.6307</v>
+      <c r="F10" s="11" t="n">
+        <v>-25.4527</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -1245,17 +1246,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E11" s="13" t="n">
+      <c r="D11" s="10" t="n">
+        <v>1.03976</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
+      <c r="F11" s="11" t="n">
+        <v>5.68238</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1274,17 +1275,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>1.01753</v>
-      </c>
-      <c r="E12" s="13" t="n">
+      <c r="D12" s="10" t="n">
+        <v>1.02279</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>1.83019</v>
+      <c r="F12" s="11" t="n">
+        <v>7.72198</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1303,17 +1304,17 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="13" t="n">
-        <v>1.02925</v>
-      </c>
-      <c r="E13" s="13" t="n">
+      <c r="D13" s="10" t="n">
+        <v>1.01344</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>-32.6977</v>
+      <c r="F13" s="11" t="n">
+        <v>-26.5374</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1332,17 +1333,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="14" t="n">
-        <v>-27.5971</v>
+      <c r="F14" s="11" t="n">
+        <v>-21.4964</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1440,19 +1441,19 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>31.9228</v>
+        <v>31.838</v>
       </c>
       <c r="E2" s="9" t="n">
-        <v>-51.2774</v>
+        <v>-54.7681</v>
       </c>
       <c r="F2" s="9" t="n">
-        <v>60.40229226279413</v>
+        <v>63.34984626350722</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>434.3988569615826</v>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>0.139048</v>
+        <v>434.3999387210523</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0.145833</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -1477,19 +1478,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-203.1</v>
+        <v>-203.999</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>-27.2272</v>
+        <v>-30.4383</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>204.9168866146468</v>
+        <v>206.2573201316501</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>434.3990388778351</v>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>0.471725</v>
+        <v>434.3996969980626</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.47481</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -1514,19 +1515,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>-182.615</v>
+        <v>-182.661</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>-24.8479</v>
+        <v>-28.0685</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>184.2977383458896</v>
+        <v>184.8049826526601</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>434.3991249352156</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>0.424259</v>
+        <v>434.3988102604209</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0.4254270000000001</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -1551,19 +1552,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-214.512</v>
+        <v>-213.589</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>-61.9892</v>
+        <v>-55.9921</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>223.2891825876032</v>
+        <v>220.8061959805703</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>868.7990793614356</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.257009</v>
+        <v>868.7992413194135</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.254151</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -1588,19 +1589,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>63.8822</v>
+        <v>63.9873</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>-14.294</v>
+        <v>-10.9719</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>65.46185082045878</v>
+        <v>64.92116104091177</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>434.3996205611253</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.150695</v>
+        <v>434.4005422610356</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.14945</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1625,19 +1626,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>50.98</v>
+        <v>51.8189</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5.76608</v>
+        <v>9.83418</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>51.30504925020927</v>
+        <v>52.74381000157648</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>434.3983307385677</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.118106</v>
+        <v>434.3986064798999</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.121418</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -1662,19 +1663,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>-356.004</v>
+        <v>-355.092</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-70.9945</v>
+        <v>-86.062</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>363.0138661900534</v>
+        <v>365.3724076993226</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>868.8013301727088</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.417833</v>
+        <v>868.8007259559494</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.420548</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -1702,16 +1703,16 @@
         <v>299.985</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>156.832</v>
+        <v>158.083</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>338.5074245108961</v>
+        <v>339.0888307125435</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>434.4004564773604</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.7792520000000001</v>
+        <v>434.4006850107528</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.78059</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -1736,19 +1737,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>-356.004</v>
+        <v>-327.839</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>83.1435</v>
+        <v>72.9327</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>365.5840390501889</v>
+        <v>335.853522611108</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1000.000106815914</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>0.365584</v>
+        <v>1000.001556070983</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.335853</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -1773,19 +1774,19 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>339.512</v>
+        <v>338.589</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>57.2949</v>
+        <v>67.764</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>344.3125087910836</v>
+        <v>345.3034471548177</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>999.9985733651753</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>0.344313</v>
+        <v>999.9983989609669</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.345304</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -1810,19 +1811,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>527.181</v>
+        <v>500</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-34.0556</v>
+        <v>-17.5972</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>528.2798412322393</v>
+        <v>500.3095656169688</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>999.9996994628591</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.5282800000000001</v>
+        <v>999.9991317722387</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.50031</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1850,16 +1851,16 @@
         <v>500</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>148.995</v>
+        <v>148.659</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>521.727428860128</v>
+        <v>521.6315733168383</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>1000.000822001024</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.5217269999999999</v>
+        <v>999.9991820226487</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.521632</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1887,16 +1888,16 @@
         <v>200</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>234.934</v>
+        <v>218.855</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>308.5352238497251</v>
+        <v>296.4751440255995</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1000.000725524576</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.308535</v>
+        <v>1000.000485793404</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.296475</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1924,16 +1925,16 @@
         <v>300</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>156.918</v>
+        <v>158.169</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>338.5605687672444</v>
+        <v>339.1422010912237</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>500.0001015582803</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>0.6771210000000001</v>
+        <v>499.9995593168413</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.678285</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1958,13 +1959,13 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
@@ -2044,37 +2045,37 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1.69625e-16</v>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="16" t="n">
-        <v>3.9846e-17</v>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>4.000000000173625e-06</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>2.9740860125e-14</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>9.961500000000001e-15</v>
-      </c>
-      <c r="K2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13" t="n">
+      <c r="B2" s="13" t="n">
+        <v>1.67514e-16</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>4.02456e-16</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>1.26017e-16</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1.199999997018953e-07</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>8.16658892352e-14</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>5.0239387392e-15</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>4.410595e-14</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -2089,37 +2090,37 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>1.87274e-15</v>
-      </c>
-      <c r="C3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>3.600000001754216e-06</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>4.960888260000002e-15</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13" t="n">
+      <c r="B3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>3.44383e-41</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2.15127e-16</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>2.000000000057511e-06</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>6.334270957300001e-39</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>5.378175e-14</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -2134,37 +2135,37 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>9.01764e-17</v>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>2.05962e-40</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>9.01764e-17</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>3.036239388000001e-15</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>3.837689946000001e-38</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13" t="n">
+      <c r="B4" s="13" t="n">
+        <v>2.35092e-16</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>2.800000000067469e-06</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>4.548560016000003e-15</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -2179,37 +2180,37 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>2.15793e-16</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>7.552755000000001e-14</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13" t="n">
+      <c r="B5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>9.714200000000001e-41</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>5.3706e-17</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>3.999999999892978e-06</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1.8233747684e-38</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>8.055900000000001e-15</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -2256,7 +2257,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>618.3480000000001</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="4">
@@ -2296,7 +2297,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>7.652000000000044</v>
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="8">
@@ -2306,7 +2307,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1128.7</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="9">
@@ -2316,7 +2317,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.825353265911752</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="10">
@@ -2336,7 +2337,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2356,7 +2357,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2365,7 +2366,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="13" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2377,7 +2378,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (77.9%)</t>
+          <t>6.0-&gt;7.0 (78.1%)</t>
         </is>
       </c>
     </row>
@@ -2429,13 +2430,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.26933</v>
+        <v>0.719973</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
@@ -2453,13 +2454,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2.29046</v>
+        <v>1.26786</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -2477,13 +2478,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.75899</v>
+        <v>2.23035</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -2501,20 +2502,20 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.85</v>
+        <v>1.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>1.76311</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,12 @@
         <bgColor rgb="00002060"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -85,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,10 +102,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -472,7 +480,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,7 +499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>solved</t>
+          <t>infeasible</t>
         </is>
       </c>
     </row>
@@ -502,7 +510,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1087.56</v>
+        <v>4.36031e-10</v>
       </c>
     </row>
     <row r="5">
@@ -522,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.2531167015847</v>
+        <v>-264.728926116823</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +540,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>614.7682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12">
@@ -582,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -602,7 +610,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +630,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17"/>
@@ -670,9 +678,9 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -738,179 +746,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>8.9875669536</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>13.8629069536</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>-4.87534</v>
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>233.19875766</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>207.36825766</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>25.8305</v>
+      <c r="D3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1.53771e-11</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>1.24389e-09</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>-1.24389e-09</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>2.23035</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>514.4346882</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>424.6742882</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>89.7604</v>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>1.76311</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>330.93927322</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>285.09097322</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>45.8483</v>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -933,7 +941,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -985,17 +993,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>1.04008</v>
-      </c>
-      <c r="E2" s="10" t="n">
+      <c r="D2" s="11" t="n">
+        <v>1.03418</v>
+      </c>
+      <c r="E2" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>2.23655</v>
+      <c r="F2" s="12" t="n">
+        <v>3.64467</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -1014,17 +1022,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <v>1.00143</v>
-      </c>
-      <c r="E3" s="10" t="n">
+      <c r="D3" s="11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E3" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>4.08351</v>
+      <c r="F3" s="12" t="n">
+        <v>7.42074</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -1043,17 +1051,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>0.984186</v>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="11" t="n">
+        <v>1.02002</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>-28.0312</v>
+      <c r="F4" s="12" t="n">
+        <v>-20.1557</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -1072,17 +1080,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E5" s="10" t="n">
+      <c r="D5" s="11" t="n">
+        <v>0.979232</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>-33.1882</v>
+      <c r="F5" s="12" t="n">
+        <v>-22.9607</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -1101,17 +1109,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>0.964028</v>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="D6" s="11" t="n">
+        <v>0.970912</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>-22.9809</v>
+      <c r="F6" s="12" t="n">
+        <v>-16.826</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -1130,17 +1138,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>1.0061</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D7" s="11" t="n">
+        <v>1.04998</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>-25.7428</v>
+      <c r="F7" s="12" t="n">
+        <v>-0.260874</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1159,17 +1167,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>1.00627</v>
-      </c>
-      <c r="E8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>-25.73</v>
+      <c r="E8" s="11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>-0.247904</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -1188,16 +1196,16 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1217,17 +1225,17 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>0.994143</v>
-      </c>
-      <c r="E10" s="10" t="n">
+      <c r="D10" s="11" t="n">
+        <v>1.03345</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>-25.4527</v>
+      <c r="F10" s="12" t="n">
+        <v>-18.3366</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -1246,17 +1254,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>1.03976</v>
-      </c>
-      <c r="E11" s="10" t="n">
+      <c r="D11" s="11" t="n">
+        <v>1.03227</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>5.68238</v>
+      <c r="F11" s="12" t="n">
+        <v>7.1354</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1275,17 +1283,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>1.02279</v>
-      </c>
-      <c r="E12" s="10" t="n">
+      <c r="D12" s="11" t="n">
+        <v>0.952461</v>
+      </c>
+      <c r="E12" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>7.72198</v>
+      <c r="F12" s="12" t="n">
+        <v>11.5402</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1304,17 +1312,17 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>1.01344</v>
-      </c>
-      <c r="E13" s="10" t="n">
+      <c r="D13" s="11" t="n">
+        <v>1.01971</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>-26.5374</v>
+      <c r="F13" s="12" t="n">
+        <v>-18.7233</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1333,17 +1341,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
+        <v>1.04736</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>-21.4964</v>
+      <c r="F14" s="12" t="n">
+        <v>3.81932</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1440,20 +1448,20 @@
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>31.838</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>-54.7681</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>63.34984626350722</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>434.3999387210523</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0.145833</v>
+      <c r="D2" s="13" t="n">
+        <v>59.2914</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>-118.197</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>132.2346434296248</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>434.4007970566536</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0.304407</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -1477,20 +1485,20 @@
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>-203.999</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>-30.4383</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>206.2573201316501</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>434.3996969980626</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>0.47481</v>
+      <c r="D3" s="13" t="n">
+        <v>-28.3003</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>10.242</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>30.09660353079729</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>434.399732269833</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>0.0692832</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -1514,20 +1522,20 @@
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>-182.661</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-28.0685</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>184.8049826526601</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>434.3988102604209</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>0.4254270000000001</v>
+      <c r="D4" s="13" t="n">
+        <v>-153.503</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>0.255597</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>153.5032127964311</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>434.4004346642342</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>0.353368</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -1551,20 +1559,20 @@
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>-213.589</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>-55.9921</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>220.8061959805703</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>868.7992413194135</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.254151</v>
+      <c r="D5" s="13" t="n">
+        <v>-132.402</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>-82.38809999999999</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>155.9425811816965</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>868.7996188225462</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>0.179492</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -1588,20 +1596,20 @@
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>63.9873</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-10.9719</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>64.92116104091177</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>434.4005422610356</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.14945</v>
+      <c r="D6" s="13" t="n">
+        <v>39.2255</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>-11.9453</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>41.00402470904532</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>434.3996413805065</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>0.0943924</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1625,20 +1633,20 @@
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>51.8189</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>9.83418</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>52.74381000157648</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>434.3986064798999</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.121418</v>
+      <c r="D7" s="13" t="n">
+        <v>155.949</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>-29.7886</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>158.7685462897485</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>434.3991526163464</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.36549</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -1662,20 +1670,20 @@
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>-355.092</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-86.062</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>365.3724076993226</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>868.8007259559494</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.420548</v>
+      <c r="D8" s="13" t="n">
+        <v>-266.262</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>-27.9156</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>267.7213726383458</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>868.7992985203545</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>0.308151</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -1699,20 +1707,20 @@
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>299.985</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>158.083</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>339.0888307125435</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>434.4006850107528</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.78059</v>
+      <c r="D9" s="13" t="n">
+        <v>299.989</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>-21.3917</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>300.75073557664</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>434.3999670342723</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.692336</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -1736,20 +1744,20 @@
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>-327.839</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>72.9327</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>335.853522611108</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1000.001556070983</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0.335853</v>
+      <c r="D10" s="13" t="n">
+        <v>-530.991</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>108.922</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>542.0474556392641</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1000.000840589956</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0.5420470000000001</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -1773,20 +1781,20 @@
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>338.589</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>67.764</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>345.3034471548177</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>999.9983989609669</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.345304</v>
+      <c r="D11" s="13" t="n">
+        <v>257.402</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>101.229</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>276.5919377801891</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>999.9997750484073</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>0.276592</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -1810,20 +1818,20 @@
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>-17.5972</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>500.3095656169688</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>999.9991317722387</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.50031</v>
+      <c r="E12" s="13" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>500.9293862412146</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1000.000771049819</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>0.500929</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1847,20 +1855,20 @@
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>148.659</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>521.6315733168383</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>999.9991820226487</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0.521632</v>
+      <c r="E13" s="13" t="n">
+        <v>2.34187e-08</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>0.5</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1884,20 +1892,20 @@
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>218.855</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>296.4751440255995</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1000.000485793404</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.296475</v>
+      <c r="E14" s="13" t="n">
+        <v>-5.00096</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>200.0625142322309</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>999.9975719259979</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>0.200063</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1921,20 +1929,20 @@
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>158.169</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>339.1422010912237</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>499.9995593168413</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0.678285</v>
+      <c r="E15" s="13" t="n">
+        <v>-21.3318</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>300.7574532596657</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>499.9999222956463</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>0.601515</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1959,14 +1967,14 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -2045,37 +2053,37 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>1.67514e-16</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>4.02456e-16</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>1.26017e-16</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>1.199999997018953e-07</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>8.16658892352e-14</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>5.0239387392e-15</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>4.410595e-14</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="10" t="n">
+      <c r="B2" s="15" t="n">
+        <v>1.724e-16</v>
+      </c>
+      <c r="C2" s="15" t="n">
+        <v>0.692491</v>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>3.33771e-16</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>0.843537</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>7.509000000000161e-05</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>6.463000000000475e-05</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>8.62e-14</v>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>1.1681985e-13</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -2090,37 +2098,37 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>3.44383e-41</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>2.15127e-16</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>2.000000000057511e-06</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>6.334270957300001e-39</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>5.378175e-14</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10" t="n">
+      <c r="B3" s="15" t="n">
+        <v>2.61243e-17</v>
+      </c>
+      <c r="C3" s="15" t="n">
+        <v>0.89244</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>1.63868e-16</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>1.14327</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>7.560000000000032e-05</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>6.730000000000104e-05</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>9.404748e-15</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>4.0967e-14</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -2135,37 +2143,37 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>2.35092e-16</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>2.800000000067469e-06</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>4.548560016000003e-15</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
+      <c r="B4" s="15" t="n">
+        <v>2.52874e-16</v>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>1.39189</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>2.30884e-16</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>1.74253</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>8.109999999999888e-05</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>7.47000000000074e-05</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>6.321850000000001e-14</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>3.925028e-14</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -2180,37 +2188,37 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>9.714200000000001e-41</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>5.3706e-17</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>3.999999999892978e-06</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>1.8233747684e-38</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>8.055900000000001e-15</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10" t="n">
+      <c r="B5" s="15" t="n">
+        <v>9.01377e-17</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>1.19213</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1.05673e-16</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>1.4928</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>7.870000000000273e-05</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>7.200000000000262e-05</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>1.9830294e-14</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>1.585095e-14</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -2257,7 +2265,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>614.7682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2297,7 +2305,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -2307,7 +2315,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1087.56</v>
+        <v>4.36031e-10</v>
       </c>
     </row>
     <row r="9">
@@ -2317,7 +2325,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2337,7 +2345,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2357,7 +2365,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2366,7 +2374,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="15" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2378,7 +2386,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (78.1%)</t>
+          <t>6.0-&gt;7.0 (69.2%)</t>
         </is>
       </c>
     </row>
@@ -2436,14 +2444,14 @@
         <v>0.85</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.719973</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2460,14 +2468,14 @@
         <v>1.15</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.26786</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2484,14 +2492,14 @@
         <v>1.75</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.23035</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2508,14 +2516,14 @@
         <v>1.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.76311</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -74,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,14 +102,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infeasible</t>
+          <t>solved</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.36031e-10</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-264.728926116823</v>
+        <v>27.2531167438279</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="8">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>626</v>
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="13">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17"/>
@@ -678,9 +678,9 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -746,179 +746,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="9" t="n">
-        <v>0</v>
+      <c r="D2" s="8" t="n">
+        <v>0.719973</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>12.4832</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>12.4832</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>8.9875669536</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>13.8629069536</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>-4.87534</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>1.53771e-11</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>1.24389e-09</v>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>-1.24389e-09</v>
+      <c r="D3" s="8" t="n">
+        <v>1.26786</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>183.931</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>183.931</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>233.19875766</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>207.36825766</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>25.8305</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>0</v>
+      <c r="D4" s="8" t="n">
+        <v>2.23035</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>514.4346882</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>424.6742882</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>89.7604</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9" t="n">
-        <v>0</v>
+      <c r="D5" s="8" t="n">
+        <v>1.76311</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>330.93927322</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>285.09097322</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>45.8483</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +941,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -993,17 +993,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="11" t="n">
-        <v>1.03418</v>
-      </c>
-      <c r="E2" s="11" t="n">
+      <c r="D2" s="10" t="n">
+        <v>1.04008</v>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="12" t="n">
-        <v>3.64467</v>
+      <c r="F2" s="11" t="n">
+        <v>2.23655</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -1022,17 +1022,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E3" s="11" t="n">
+      <c r="D3" s="10" t="n">
+        <v>1.00143</v>
+      </c>
+      <c r="E3" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="12" t="n">
-        <v>7.42074</v>
+      <c r="F3" s="11" t="n">
+        <v>4.08351</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -1051,17 +1051,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>1.02002</v>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="D4" s="10" t="n">
+        <v>0.984186</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <v>-20.1557</v>
+      <c r="F4" s="11" t="n">
+        <v>-28.0312</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -1080,17 +1080,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>0.979232</v>
-      </c>
-      <c r="E5" s="11" t="n">
+      <c r="D5" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>-22.9607</v>
+      <c r="F5" s="11" t="n">
+        <v>-33.1882</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -1109,17 +1109,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="11" t="n">
-        <v>0.970912</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="D6" s="10" t="n">
+        <v>0.964028</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>-16.826</v>
+      <c r="F6" s="11" t="n">
+        <v>-22.9809</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -1138,17 +1138,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>1.04998</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="10" t="n">
+        <v>1.0061</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="12" t="n">
-        <v>-0.260874</v>
+      <c r="F7" s="11" t="n">
+        <v>-25.7428</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1167,17 +1167,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
+        <v>1.00627</v>
+      </c>
+      <c r="E8" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>-0.247904</v>
+      <c r="F8" s="11" t="n">
+        <v>-25.73</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -1196,16 +1196,16 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1225,17 +1225,17 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="11" t="n">
-        <v>1.03345</v>
-      </c>
-      <c r="E10" s="11" t="n">
+      <c r="D10" s="10" t="n">
+        <v>0.994143</v>
+      </c>
+      <c r="E10" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="12" t="n">
-        <v>-18.3366</v>
+      <c r="F10" s="11" t="n">
+        <v>-25.4527</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -1254,17 +1254,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>1.03227</v>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="D11" s="10" t="n">
+        <v>1.03976</v>
+      </c>
+      <c r="E11" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="12" t="n">
-        <v>7.1354</v>
+      <c r="F11" s="11" t="n">
+        <v>5.68238</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1283,17 +1283,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>0.952461</v>
-      </c>
-      <c r="E12" s="11" t="n">
+      <c r="D12" s="10" t="n">
+        <v>1.02279</v>
+      </c>
+      <c r="E12" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="12" t="n">
-        <v>11.5402</v>
+      <c r="F12" s="11" t="n">
+        <v>7.72198</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1312,17 +1312,17 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>1.01971</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="D13" s="10" t="n">
+        <v>1.01344</v>
+      </c>
+      <c r="E13" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>-18.7233</v>
+      <c r="F13" s="11" t="n">
+        <v>-26.5374</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1341,17 +1341,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="10" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>1.04736</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="D14" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>3.81932</v>
+      <c r="E14" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>-21.4964</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1448,20 +1448,20 @@
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>59.2914</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>-118.197</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>132.2346434296248</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>434.4007970566536</v>
-      </c>
-      <c r="H2" s="14" t="n">
-        <v>0.304407</v>
+      <c r="D2" s="9" t="n">
+        <v>31.838</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>-54.7681</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>63.34984626350722</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>434.3999387210523</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0.145833</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -1485,20 +1485,20 @@
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>-28.3003</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>10.242</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>30.09660353079729</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>434.399732269833</v>
-      </c>
-      <c r="H3" s="14" t="n">
-        <v>0.0692832</v>
+      <c r="D3" s="9" t="n">
+        <v>-203.999</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>-30.4383</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>206.2573201316501</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>434.3996969980626</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.47481</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -1522,20 +1522,20 @@
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>-153.503</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>0.255597</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>153.5032127964311</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>434.4004346642342</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>0.353368</v>
+      <c r="D4" s="9" t="n">
+        <v>-182.661</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-28.0685</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>184.8049826526601</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>434.3988102604209</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0.4254270000000001</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -1559,20 +1559,20 @@
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>-132.402</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>-82.38809999999999</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>155.9425811816965</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>868.7996188225462</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>0.179492</v>
+      <c r="D5" s="9" t="n">
+        <v>-213.589</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>-55.9921</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>220.8061959805703</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>868.7992413194135</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.254151</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -1596,20 +1596,20 @@
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>39.2255</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>-11.9453</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>41.00402470904532</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>434.3996413805065</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>0.0943924</v>
+      <c r="D6" s="9" t="n">
+        <v>63.9873</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-10.9719</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>64.92116104091177</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>434.4005422610356</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.14945</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1633,20 +1633,20 @@
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>155.949</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>-29.7886</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>158.7685462897485</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>434.3991526163464</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>0.36549</v>
+      <c r="D7" s="9" t="n">
+        <v>51.8189</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>9.83418</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>52.74381000157648</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>434.3986064798999</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.121418</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -1670,20 +1670,20 @@
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>-266.262</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>-27.9156</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>267.7213726383458</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>868.7992985203545</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0.308151</v>
+      <c r="D8" s="9" t="n">
+        <v>-355.092</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-86.062</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>365.3724076993226</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>868.8007259559494</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.420548</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -1707,20 +1707,20 @@
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>299.989</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>-21.3917</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>300.75073557664</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>434.3999670342723</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>0.692336</v>
+      <c r="D9" s="9" t="n">
+        <v>299.985</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>158.083</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>339.0888307125435</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>434.4006850107528</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.78059</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -1744,20 +1744,20 @@
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>-530.991</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>108.922</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>542.0474556392641</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>1000.000840589956</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0.5420470000000001</v>
+      <c r="D10" s="9" t="n">
+        <v>-327.839</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>72.9327</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>335.853522611108</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1000.001556070983</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.335853</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -1781,20 +1781,20 @@
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>257.402</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>101.229</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>276.5919377801891</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>999.9997750484073</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>0.276592</v>
+      <c r="D11" s="9" t="n">
+        <v>338.589</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>67.764</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>345.3034471548177</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>999.9983989609669</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.345304</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -1818,20 +1818,20 @@
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>500.9293862412146</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>1000.000771049819</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>0.500929</v>
+      <c r="E12" s="9" t="n">
+        <v>-17.5972</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>500.3095656169688</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>999.9991317722387</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.50031</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1855,20 +1855,20 @@
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="13" t="n">
-        <v>2.34187e-08</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>0.5</v>
+      <c r="E13" s="9" t="n">
+        <v>148.659</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>521.6315733168383</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>999.9991820226487</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.521632</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1892,20 +1892,20 @@
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="13" t="n">
-        <v>-5.00096</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>200.0625142322309</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>999.9975719259979</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>0.200063</v>
+      <c r="E14" s="9" t="n">
+        <v>218.855</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>296.4751440255995</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1000.000485793404</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.296475</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1929,20 +1929,20 @@
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="13" t="n">
-        <v>-21.3318</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>300.7574532596657</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>499.9999222956463</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>0.601515</v>
+      <c r="E15" s="9" t="n">
+        <v>158.169</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>339.1422010912237</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>499.9995593168413</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.678285</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1967,14 +1967,14 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -2053,42 +2053,42 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n">
-        <v>1.724e-16</v>
-      </c>
-      <c r="C2" s="15" t="n">
-        <v>0.692491</v>
-      </c>
-      <c r="D2" s="15" t="n">
-        <v>3.33771e-16</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>0.843537</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>7.509000000000161e-05</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <v>6.463000000000475e-05</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>8.62e-14</v>
-      </c>
-      <c r="I2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>1.1681985e-13</v>
-      </c>
-      <c r="K2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>4.02456e-16</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>0.781049</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1.199999995517285e-09</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0.0006895100000000008</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="n">
+        <v>5.0239387392e-15</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2098,42 +2098,42 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
-        <v>2.61243e-17</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>0.89244</v>
-      </c>
-      <c r="D3" s="15" t="n">
-        <v>1.63868e-16</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>1.14327</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>7.560000000000032e-05</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>6.730000000000104e-05</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>9.404748e-15</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>4.0967e-14</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B3" s="13" t="n">
+        <v>5.3003e-18</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>3.4772e-17</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>1.07548</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>2.000000000166895e-08</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0.0007451999999999997</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>9.332185206999999e-16</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>8.693e-15</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2143,42 +2143,42 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
-        <v>2.52874e-16</v>
-      </c>
-      <c r="C4" s="15" t="n">
-        <v>1.39189</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>2.30884e-16</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>1.74253</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>8.109999999999888e-05</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>7.47000000000074e-05</v>
-      </c>
-      <c r="H4" s="11" t="n">
-        <v>6.321850000000001e-14</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>3.925028e-14</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B4" s="13" t="n">
+        <v>3.51477e-16</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>6.03546e-26</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1.66601</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>2.79999999990945e-08</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.0008399000000000011</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>6.800376996000004e-15</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>1.39209091992e-23</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2188,42 +2188,42 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>9.01377e-17</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>1.19213</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>1.05673e-16</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>1.4928</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>7.870000000000273e-05</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>7.200000000000262e-05</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>1.9830294e-14</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>1.585095e-14</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B5" s="13" t="n">
+        <v>3.65336e-17</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1.0873e-16</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1.41985</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>3.999999999939711e-08</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.0008015000000000001</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1.179962212800001e-15</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>1.63095e-14</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="4">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>626</v>
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="8">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4.36031e-10</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="9">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="10">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="13" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (69.2%)</t>
+          <t>6.0-&gt;7.0 (78.1%)</t>
         </is>
       </c>
     </row>
@@ -2444,14 +2444,14 @@
         <v>0.85</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0</v>
+        <v>0.719973</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2468,14 +2468,14 @@
         <v>1.15</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>1.26786</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2492,14 +2492,14 @@
         <v>1.75</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>2.23035</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2516,14 +2516,14 @@
         <v>1.5</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>1.76311</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +62,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,8 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,14 +108,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +489,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>solved</t>
+          <t>infeasible</t>
         </is>
       </c>
     </row>
@@ -510,7 +519,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1087.56</v>
+        <v>3.74564e-10</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.2531167438279</v>
+        <v>-264.728926116821</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +549,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>614.7682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -580,7 +589,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>626</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +599,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -610,7 +619,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +639,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17"/>
@@ -650,7 +659,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>INVALID (solver did not converge)</t>
         </is>
       </c>
     </row>
@@ -678,8 +687,8 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -746,179 +755,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>8.9875669536</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>13.8629069536</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>-4.87534</v>
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>233.19875766</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>207.36825766</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>25.8305</v>
+      <c r="D3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1.53782e-11</v>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>2.23035</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>514.4346882</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>424.6742882</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>89.7604</v>
+      <c r="D4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>1.76311</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>330.93927322</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>285.09097322</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>45.8483</v>
+      <c r="D5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +950,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -983,377 +992,377 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>1.04008</v>
-      </c>
-      <c r="E2" s="10" t="n">
+      <c r="D2" s="13" t="n">
+        <v>1.03418</v>
+      </c>
+      <c r="E2" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>2.23655</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="F2" s="14" t="n">
+        <v>3.64467</v>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="10" t="n">
+      <c r="C3" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="10" t="n">
-        <v>1.00143</v>
-      </c>
-      <c r="E3" s="10" t="n">
+      <c r="D3" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>4.08351</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="F3" s="14" t="n">
+        <v>7.42074</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="10" t="n">
-        <v>0.984186</v>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" s="13" t="n">
+        <v>1.02002</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>-28.0312</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="F4" s="14" t="n">
+        <v>-20.1557</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="13" t="n">
+        <v>0.979232</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>-22.9607</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="D6" s="13" t="n">
+        <v>0.970912</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>-33.1882</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
+      <c r="F6" s="14" t="n">
+        <v>-16.826</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="10" t="n">
-        <v>0.964028</v>
-      </c>
-      <c r="E6" s="10" t="n">
+      <c r="D7" s="13" t="n">
+        <v>1.04998</v>
+      </c>
+      <c r="E7" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>-22.9809</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
+      <c r="F7" s="14" t="n">
+        <v>-0.260874</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>1.0061</v>
-      </c>
-      <c r="E7" s="10" t="n">
+      <c r="D8" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>-25.7428</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
+      <c r="E8" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>-0.247904</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>1.00627</v>
-      </c>
-      <c r="E8" s="10" t="n">
+      <c r="D9" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>-25.73</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
+      <c r="E9" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D10" s="13" t="n">
+        <v>1.03345</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="F10" s="14" t="n">
+        <v>-18.3366</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>1.03227</v>
+      </c>
+      <c r="E11" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
+      <c r="F11" s="14" t="n">
+        <v>7.1354</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>0.994143</v>
-      </c>
-      <c r="E10" s="10" t="n">
+      <c r="D12" s="13" t="n">
+        <v>0.952461</v>
+      </c>
+      <c r="E12" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>-25.4527</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="F12" s="14" t="n">
+        <v>11.5402</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>1.03976</v>
-      </c>
-      <c r="E11" s="10" t="n">
+      <c r="D13" s="13" t="n">
+        <v>1.01971</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>5.68238</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
+      <c r="F13" s="14" t="n">
+        <v>-18.7233</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>1.02279</v>
-      </c>
-      <c r="E12" s="10" t="n">
+      <c r="D14" s="13" t="n">
+        <v>1.04736</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>7.72198</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>1.01344</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>-26.5374</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>-21.4964</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="14" t="n">
+        <v>3.81932</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1433,518 +1442,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>31.838</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>-54.7681</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>63.34984626350722</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>434.3999387210523</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0.145833</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="D2" s="15" t="n">
+        <v>59.2914</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>-118.197</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>132.2346434296248</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>434.4007970566536</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <v>0.304407</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>-203.999</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>-30.4383</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>206.2573201316501</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>434.3996969980626</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>0.47481</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="D3" s="15" t="n">
+        <v>-28.3003</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>10.242</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>30.09660353079729</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>434.399732269833</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>0.0692832</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>-182.661</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-28.0685</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>184.8049826526601</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>434.3988102604209</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>0.4254270000000001</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="D4" s="15" t="n">
+        <v>-153.503</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.255597</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>153.5032127964311</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>434.4004346642342</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.353368</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>-213.589</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>-55.9921</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>220.8061959805703</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>868.7992413194135</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.254151</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="D5" s="15" t="n">
+        <v>-132.402</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-82.38809999999999</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>155.9425811816965</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>868.7996188225462</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.179492</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>63.9873</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-10.9719</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>64.92116104091177</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>434.4005422610356</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.14945</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="D6" s="15" t="n">
+        <v>39.2255</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-11.9453</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>41.00402470904532</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>434.3996413805065</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.0943924</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>51.8189</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>9.83418</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>52.74381000157648</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>434.3986064798999</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.121418</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="D7" s="15" t="n">
+        <v>155.949</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-29.7886</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>158.7685462897485</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>434.3991526163464</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>-355.092</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-86.062</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>365.3724076993226</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>868.8007259559494</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.420548</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="D8" s="15" t="n">
+        <v>-266.262</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-27.9156</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>267.7213726383458</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>868.7992985203545</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.308151</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>299.985</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>158.083</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>339.0888307125435</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>434.4006850107528</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.78059</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="D9" s="15" t="n">
+        <v>299.989</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-21.3917</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>300.75073557664</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>434.3999670342723</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.692336</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>-327.839</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>72.9327</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>335.853522611108</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1000.001556070983</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0.335853</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>-530.991</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>108.922</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>542.0474556392641</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>1000.000840589956</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.5420470000000001</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>338.589</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>67.764</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>345.3034471548177</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>999.9983989609669</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.345304</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>257.402</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>101.229</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>276.5919377801891</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>999.9997750484073</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.276592</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>-17.5972</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>500.3095656169688</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>999.9991317722387</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.50031</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="E12" s="15" t="n">
+        <v>-30.5</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>500.9293862412146</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1000.000771049819</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.500929</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>148.659</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>521.6315733168383</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>999.9991820226487</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0.521632</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="E13" s="15" t="n">
+        <v>2.34187e-08</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>218.855</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>296.4751440255995</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1000.000485793404</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.296475</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="E14" s="15" t="n">
+        <v>-5.00096</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>200.0625142322309</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>999.9975719259979</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0.200063</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>158.169</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>339.1422010912237</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>499.9995593168413</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0.678285</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="E15" s="15" t="n">
+        <v>-21.3318</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>300.7574532596657</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>499.9999222956463</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.601515</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1967,11 +1976,11 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2053,42 +2062,42 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>4.02456e-16</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>0.781049</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>1.199999995517285e-09</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>0.0006895100000000008</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>5.0239387392e-15</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="15" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B2" s="17" t="n">
+        <v>3.95709e-16</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>0.693557</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>2.41588e-16</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>0.843537</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>0.006443000000000421</v>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>0.006463000000000219</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>1.978545e-13</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>8.455580000000001e-14</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2098,42 +2107,42 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>5.3003e-18</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>3.4772e-17</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>1.07548</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>2.000000000166895e-08</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>0.0007451999999999997</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>9.332185206999999e-16</v>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="10" t="n">
-        <v>8.693e-15</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="15" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B3" s="17" t="n">
+        <v>1.13369e-17</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>0.893526</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>3.15401e-16</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>1.14327</v>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>0.00647399999999998</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0.006730000000000125</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>4.081284e-15</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>7.885025000000001e-14</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2143,42 +2152,42 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>3.51477e-16</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>6.03546e-26</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>1.66601</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>2.79999999990945e-08</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.0008399000000000011</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>6.800376996000004e-15</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1.39209091992e-23</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B4" s="17" t="n">
+        <v>3.27749e-16</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>1.39292</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>2.64142e-16</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>1.74253</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>0.007080000000000197</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.00747000000000031</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>8.193724999999999e-14</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>4.490414e-14</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2188,42 +2197,42 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>3.65336e-17</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>1.0873e-16</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1.41985</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>3.999999999939711e-08</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.0008015000000000001</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>1.179962212800001e-15</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>1.63095e-14</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B5" s="17" t="n">
+        <v>1.3933e-16</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>1.19319</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>1.34944e-16</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>1.4928</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.006810000000000205</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.007200000000000317</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>3.06526e-14</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>2.02416e-14</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2256,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2265,7 +2274,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>614.7682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2305,7 +2314,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -2315,7 +2324,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1087.56</v>
+        <v>3.74564e-10</v>
       </c>
     </row>
     <row r="9">
@@ -2325,7 +2334,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2345,7 +2354,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2365,7 +2374,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2383,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="17" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2386,7 +2395,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (78.1%)</t>
+          <t>6.0-&gt;7.0 (69.2%)</t>
         </is>
       </c>
     </row>
@@ -2443,15 +2452,15 @@
       <c r="C20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2467,15 +2476,15 @@
       <c r="C21" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2491,15 +2500,15 @@
       <c r="C22" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>2.23035</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2515,15 +2524,15 @@
       <c r="C23" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>1.76311</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=DB</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -62,8 +62,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,17 +108,15 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +487,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infeasible</t>
+          <t>solved</t>
         </is>
       </c>
     </row>
@@ -519,7 +517,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3.74564e-10</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="5">
@@ -539,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-264.728926116821</v>
+        <v>27.25311674395</v>
       </c>
     </row>
     <row r="7">
@@ -549,7 +547,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +587,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>626</v>
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="12">
@@ -599,7 +597,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +617,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -639,7 +637,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17"/>
@@ -659,7 +657,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>INVALID (solver did not converge)</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -687,9 +685,9 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,179 +753,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>0</v>
+      <c r="D2" s="8" t="n">
+        <v>0.719973</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>12.4832</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>12.4832</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>8.9875669536</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>13.82316870541562</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>-4.835601751815624</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10" t="n">
-        <v>1.53782e-11</v>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>0</v>
+      <c r="D3" s="8" t="n">
+        <v>1.26786</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>183.931</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>183.931</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>233.19875766</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>207.3641656673038</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>25.83459199269618</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11" t="n">
-        <v>0</v>
+      <c r="D4" s="8" t="n">
+        <v>2.23035</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>230.652</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>514.4346882</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>424.6708209930521</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>89.76386720694785</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0</v>
+      <c r="D5" s="8" t="n">
+        <v>1.76311</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>187.702</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>330.93927322</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>285.0867338761526</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>45.85253934384735</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +948,7 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -992,377 +990,377 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>1.03418</v>
-      </c>
-      <c r="E2" s="13" t="n">
+      <c r="D2" s="8" t="n">
+        <v>1.04008</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="14" t="n">
-        <v>3.64467</v>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="n">
+        <v>2.23655</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="8" t="n">
+        <v>1.00143</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>4.08351</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="D4" s="8" t="n">
+        <v>0.984186</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>7.42074</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="n">
+      <c r="F4" s="11" t="n">
+        <v>-28.0312</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>1.02002</v>
-      </c>
-      <c r="E4" s="13" t="n">
+      <c r="D5" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>-20.1557</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n">
+      <c r="F5" s="11" t="n">
+        <v>-33.1882</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>0.979232</v>
-      </c>
-      <c r="E5" s="13" t="n">
+      <c r="D6" s="8" t="n">
+        <v>0.964028</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>-22.9607</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="n">
+      <c r="F6" s="11" t="n">
+        <v>-22.9809</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>0.970912</v>
-      </c>
-      <c r="E6" s="13" t="n">
+      <c r="D7" s="8" t="n">
+        <v>1.0061</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>-16.826</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n">
+      <c r="F7" s="11" t="n">
+        <v>-25.7428</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>1.04998</v>
-      </c>
-      <c r="E7" s="13" t="n">
+      <c r="D8" s="8" t="n">
+        <v>1.00627</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>-0.260874</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="F8" s="11" t="n">
+        <v>-25.73</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D9" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E9" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="14" t="n">
-        <v>-0.247904</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="n">
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D10" s="8" t="n">
+        <v>0.994143</v>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="F10" s="11" t="n">
+        <v>-25.4527</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>1.03976</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="F11" s="11" t="n">
+        <v>5.68238</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>1.03345</v>
-      </c>
-      <c r="E10" s="13" t="n">
+      <c r="D12" s="8" t="n">
+        <v>1.02279</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>-18.3366</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="n">
+      <c r="F12" s="11" t="n">
+        <v>7.72198</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>1.03227</v>
-      </c>
-      <c r="E11" s="13" t="n">
+      <c r="D13" s="8" t="n">
+        <v>1.01344</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>7.1354</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="F13" s="11" t="n">
+        <v>-26.5374</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>0.952461</v>
-      </c>
-      <c r="E12" s="13" t="n">
+      <c r="D14" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>11.5402</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>1.01971</v>
-      </c>
-      <c r="E13" s="13" t="n">
+      <c r="E14" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="14" t="n">
-        <v>-18.7233</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>1.04736</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>3.81932</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="n">
+        <v>-21.4964</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1442,518 +1440,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n">
-        <v>59.2914</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>-118.197</v>
-      </c>
-      <c r="F2" s="15" t="n">
-        <v>132.2346434296248</v>
-      </c>
-      <c r="G2" s="15" t="n">
-        <v>434.4007970566536</v>
-      </c>
-      <c r="H2" s="16" t="n">
-        <v>0.304407</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="D2" s="9" t="n">
+        <v>31.838</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>-54.7681</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>63.34984626350722</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>434.3999387210523</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0.145833</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
-        <v>-28.3003</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>10.242</v>
-      </c>
-      <c r="F3" s="15" t="n">
-        <v>30.09660353079729</v>
-      </c>
-      <c r="G3" s="15" t="n">
-        <v>434.399732269833</v>
-      </c>
-      <c r="H3" s="16" t="n">
-        <v>0.0692832</v>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="D3" s="9" t="n">
+        <v>-203.999</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>-30.4383</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>206.2573201316501</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>434.3996969980626</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
-        <v>-153.503</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.255597</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>153.5032127964311</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>434.4004346642342</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.353368</v>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="n">
+        <v>-182.661</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-28.0685</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>184.8049826526601</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>434.3988102604209</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0.4254270000000001</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
-        <v>-132.402</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-82.38809999999999</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>155.9425811816965</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>868.7996188225462</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>0.179492</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="D5" s="9" t="n">
+        <v>-213.589</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>-55.9921</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>220.8061959805703</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>868.7992413194135</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.254151</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>39.2255</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-11.9453</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>41.00402470904532</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>434.3996413805065</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.0943924</v>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="D6" s="9" t="n">
+        <v>63.9873</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-10.9719</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>64.92116104091177</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>434.4005422610356</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.14945</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
-        <v>155.949</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>-29.7886</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>158.7685462897485</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>434.3991526163464</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.36549</v>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="D7" s="9" t="n">
+        <v>51.8189</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>9.83418</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>52.74381000157648</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>434.3986064798999</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.121418</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>-266.262</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-27.9156</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>267.7213726383458</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>868.7992985203545</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0.308151</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="D8" s="9" t="n">
+        <v>-355.092</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-86.062</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>365.3724076993226</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>868.8007259559494</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.420548</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>299.989</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-21.3917</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>300.75073557664</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>434.3999670342723</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.692336</v>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="D9" s="9" t="n">
+        <v>299.985</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>158.083</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>339.0888307125435</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>434.4006850107528</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.78059</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
-        <v>-530.991</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>108.922</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>542.0474556392641</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>1000.000840589956</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>0.5420470000000001</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="D10" s="9" t="n">
+        <v>-327.839</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>72.9327</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>335.853522611108</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1000.001556070983</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.335853</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>257.402</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>101.229</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>276.5919377801891</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>999.9997750484073</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.276592</v>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="D11" s="9" t="n">
+        <v>338.589</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>67.764</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>345.3034471548177</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>999.9983989609669</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.345304</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="15" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>500.9293862412146</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>1000.000771049819</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>0.500929</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="E12" s="9" t="n">
+        <v>-17.5972</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>500.3095656169688</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>999.9991317722387</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="15" t="n">
-        <v>2.34187e-08</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="E13" s="9" t="n">
+        <v>148.659</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>521.6315733168383</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>999.9991820226487</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.521632</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="15" t="n">
-        <v>-5.00096</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>200.0625142322309</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>999.9975719259979</v>
-      </c>
-      <c r="H14" s="16" t="n">
-        <v>0.200063</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="E14" s="9" t="n">
+        <v>218.855</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>296.4751440255995</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1000.000485793404</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.296475</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>-21.3318</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>300.7574532596657</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>499.9999222956463</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>0.601515</v>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="E15" s="9" t="n">
+        <v>158.169</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>339.1422010912237</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>499.9995593168413</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.678285</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1976,11 +1974,11 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2062,40 +2060,40 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>3.95709e-16</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>0.693557</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>2.41588e-16</v>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>0.843537</v>
-      </c>
-      <c r="F2" s="18" t="n">
-        <v>0.006443000000000421</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>0.006463000000000219</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>1.978545e-13</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>8.455580000000001e-14</v>
-      </c>
-      <c r="K2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="B2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>4.02456e-16</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>0.845743</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>1.199999995343813e-07</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0.004256999999999955</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>5.0239387392e-15</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2107,40 +2105,40 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v>1.13369e-17</v>
-      </c>
-      <c r="C3" s="17" t="n">
-        <v>0.893526</v>
-      </c>
-      <c r="D3" s="17" t="n">
-        <v>3.15401e-16</v>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>1.14327</v>
-      </c>
-      <c r="F3" s="18" t="n">
-        <v>0.00647399999999998</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>0.006730000000000125</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>4.081284e-15</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>7.885025000000001e-14</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>1.4013e-45</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>1.14574</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>2.000000000057511e-06</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0.004259999999999931</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2.577425103e-43</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2152,40 +2150,40 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
-        <v>3.27749e-16</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>1.39292</v>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>2.64142e-16</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>1.74253</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <v>0.007080000000000197</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>0.00747000000000031</v>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>8.193724999999999e-14</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>4.490414e-14</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="n">
+        <v>4.66281e-16</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1.74574</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2.799999999836279e-06</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.004259999999999931</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>9.021604788000006e-15</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2197,40 +2195,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>1.3933e-16</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>1.19319</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>1.34944e-16</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>1.4928</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.006810000000000205</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.007200000000000317</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>3.06526e-14</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>2.02416e-14</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>7.32614e-17</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1.49574</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>3.999999999892978e-06</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.004259999999999931</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1.098921e-14</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2256,7 +2254,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2274,7 +2272,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>0</v>
+        <v>614.7682</v>
       </c>
     </row>
     <row r="4">
@@ -2314,7 +2312,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>626</v>
+        <v>11.23180000000002</v>
       </c>
     </row>
     <row r="8">
@@ -2324,7 +2322,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3.74564e-10</v>
+        <v>1087.56</v>
       </c>
     </row>
     <row r="9">
@@ -2334,7 +2332,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1.76905748546135</v>
       </c>
     </row>
     <row r="10">
@@ -2354,7 +2352,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2374,7 +2372,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2383,7 +2381,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="13" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2395,7 +2393,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (69.2%)</t>
+          <t>6.0-&gt;7.0 (78.1%)</t>
         </is>
       </c>
     </row>
@@ -2452,15 +2450,15 @@
       <c r="C20" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=DB</t>
+      <c r="D20" s="13" t="n">
+        <v>0.719973</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2476,15 +2474,15 @@
       <c r="C21" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=DB</t>
+      <c r="D21" s="13" t="n">
+        <v>1.26786</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2500,15 +2498,15 @@
       <c r="C22" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=DB</t>
+      <c r="D22" s="13" t="n">
+        <v>2.23035</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2524,15 +2522,15 @@
       <c r="C23" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=DB</t>
+      <c r="D23" s="13" t="n">
+        <v>1.76311</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
         </is>
       </c>
     </row>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="6">
@@ -97,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +120,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -537,7 +542,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.25311674395</v>
+        <v>27.2531167438279</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +692,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,10 +795,10 @@
         <v>8.9875669536</v>
       </c>
       <c r="K2" s="10" t="n">
-        <v>13.82316870541562</v>
+        <v>8.862904225791999</v>
       </c>
       <c r="L2" s="10" t="n">
-        <v>-4.835601751815624</v>
+        <v>0.1246627278080013</v>
       </c>
     </row>
     <row r="3">
@@ -834,10 +839,10 @@
         <v>233.19875766</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>207.3641656673038</v>
+        <v>199.368512761</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>25.83459199269618</v>
+        <v>33.83024489900001</v>
       </c>
     </row>
     <row r="4">
@@ -878,10 +883,10 @@
         <v>514.4346882</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>424.6708209930521</v>
+        <v>418.6734211871999</v>
       </c>
       <c r="L4" s="10" t="n">
-        <v>89.76386720694785</v>
+        <v>95.76126701280003</v>
       </c>
     </row>
     <row r="5">
@@ -922,10 +927,10 @@
         <v>330.93927322</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>285.0867338761526</v>
+        <v>278.090461206</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>45.85253934384735</v>
+        <v>52.84881201399998</v>
       </c>
     </row>
   </sheetData>
@@ -1975,10 +1980,10 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -2070,13 +2075,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>0.845743</v>
+        <v>0.781049</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>1.199999995343813e-07</v>
       </c>
       <c r="G2" s="14" t="n">
-        <v>0.004256999999999955</v>
+        <v>0.06895099999999998</v>
       </c>
       <c r="H2" s="8" t="n">
         <v>0</v>
@@ -2106,31 +2111,31 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>0</v>
+        <v>5.3003e-18</v>
       </c>
       <c r="C3" s="13" t="n">
-        <v>1.4013e-45</v>
+        <v>0</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>0</v>
+        <v>3.4772e-17</v>
       </c>
       <c r="E3" s="13" t="n">
-        <v>1.14574</v>
+        <v>1.07548</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>2.000000000057511e-06</v>
+        <v>2.000000000062812e-06</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>0.004259999999999931</v>
+        <v>0.07451999999999992</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>0</v>
+        <v>9.332185206999999e-16</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>2.577425103e-43</v>
+        <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
-        <v>0</v>
+        <v>8.693e-15</v>
       </c>
       <c r="K3" s="8" t="n">
         <v>0</v>
@@ -2151,28 +2156,28 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>4.66281e-16</v>
+        <v>3.51477e-16</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>0</v>
+        <v>6.03546e-26</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>1.74574</v>
+        <v>1.66601</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>2.799999999836279e-06</v>
+        <v>2.799999999951083e-06</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0.004259999999999931</v>
+        <v>0.08399000000000001</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>9.021604788000006e-15</v>
+        <v>6.800376996000004e-15</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>0</v>
+        <v>1.39209091992e-23</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>0</v>
@@ -2196,31 +2201,31 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0</v>
+        <v>3.65336e-17</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>7.32614e-17</v>
+        <v>1.0873e-16</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>1.49574</v>
+        <v>1.41985</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>3.999999999892978e-06</v>
+        <v>3.999999999856445e-06</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0.004259999999999931</v>
+        <v>0.08014999999999994</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>1.179962212800001e-15</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>1.098921e-14</v>
+        <v>1.63095e-14</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>0</v>
@@ -2246,10 +2251,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
@@ -2407,104 +2412,71 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>gen_id</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>injection_deadband_price (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>absorption_deadband_price (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>actual_lam_inj (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>actual_lam_abs (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>in_deadband?</t>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D20" s="13" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
+          <t>gen_id</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>injection_deadband_price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>absorption_deadband_price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>actual_lam_inj (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>actual_lam_abs (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>in_deadband?</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
-        </is>
-      </c>
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.75</v>
+        <v>0.85</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>2.23035</v>
+        <v>0.719973</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="17" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2513,22 +2485,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>1.26786</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>2.23035</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B25" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C25" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D25" s="13" t="n">
         <v>1.76311</v>
       </c>
-      <c r="E23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="E25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +66,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,8 +78,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -101,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,16 +124,23 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +511,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>solved</t>
+          <t>infeasible</t>
         </is>
       </c>
     </row>
@@ -522,7 +541,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1087.56</v>
+        <v>4779.62</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +561,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.2531167438279</v>
+        <v>-76.2609600100258</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +571,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>614.7682</v>
+        <v>698.98</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +581,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>121.545</v>
       </c>
     </row>
     <row r="9">
@@ -592,7 +611,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>48.56499999999998</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +621,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>6.647900057226243</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +631,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1.09309</v>
       </c>
     </row>
     <row r="14">
@@ -622,7 +641,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -632,7 +651,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -662,7 +681,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>INVALID (solver did not converge)</t>
         </is>
       </c>
     </row>
@@ -689,10 +708,10 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,179 +777,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>12.4832</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>1.09309</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>121.545</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>-121.545</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>ABSORPTION</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>132.85962405</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>118.086437025</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>14.77318702499998</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>1.44088</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>270.44</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>270.44</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J2" s="10" t="n">
-        <v>8.9875669536</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>8.862904225791999</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>0.1246627278080013</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>183.931</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="J3" s="15" t="n">
+        <v>389.6715872</v>
+      </c>
+      <c r="K3" s="15" t="n">
+        <v>316.5337936</v>
+      </c>
+      <c r="L3" s="15" t="n">
+        <v>73.13779359999995</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>15.7888</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="10" t="n">
-        <v>233.19875766</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>199.368512761</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>33.83024489900001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>2.23035</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>230.652</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="J4" s="15" t="n">
+        <v>3947.2</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>3484.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1.73562</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>178.54</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>178.54</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n">
-        <v>514.4346882</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>418.6734211871999</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>95.76126701280003</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1.76311</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>187.702</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>330.93927322</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>278.090461206</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>52.84881201399998</v>
+      <c r="J5" s="15" t="n">
+        <v>309.8775948</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>262.0627974</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>47.81479740000003</v>
       </c>
     </row>
   </sheetData>
@@ -995,377 +1014,377 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>1.04008</v>
-      </c>
-      <c r="E2" s="8" t="n">
+      <c r="D2" s="13" t="n">
+        <v>0.986374</v>
+      </c>
+      <c r="E2" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>2.23655</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="F2" s="16" t="n">
+        <v>2.97628</v>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>1.00143</v>
-      </c>
-      <c r="E3" s="8" t="n">
+      <c r="D3" s="13" t="n">
+        <v>1.0184</v>
+      </c>
+      <c r="E3" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>4.08351</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="F3" s="16" t="n">
+        <v>4.38349</v>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>0.984186</v>
-      </c>
-      <c r="E4" s="8" t="n">
+      <c r="D4" s="13" t="n">
+        <v>0.982815</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>-28.0312</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="F4" s="16" t="n">
+        <v>-26.5471</v>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>-33.1882</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="F5" s="16" t="n">
+        <v>-30.8306</v>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>0.964028</v>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="D6" s="13" t="n">
+        <v>0.978776</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>-22.9809</v>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="F6" s="16" t="n">
+        <v>-21.2808</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>1.0061</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="D7" s="13" t="n">
+        <v>1.00835</v>
+      </c>
+      <c r="E7" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>-25.7428</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="16" t="n">
+        <v>-17.6941</v>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>1.00627</v>
-      </c>
-      <c r="E8" s="8" t="n">
+      <c r="D8" s="13" t="n">
+        <v>1.00853</v>
+      </c>
+      <c r="E8" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>-25.73</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="F8" s="16" t="n">
+        <v>-17.677</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0.990121</v>
+      </c>
+      <c r="E10" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F10" s="16" t="n">
+        <v>-24.2218</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>0.994143</v>
-      </c>
-      <c r="E10" s="8" t="n">
+      <c r="D11" s="13" t="n">
+        <v>0.967757</v>
+      </c>
+      <c r="E11" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>-25.4527</v>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="F11" s="16" t="n">
+        <v>6.88077</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>1.03976</v>
-      </c>
-      <c r="E11" s="8" t="n">
+      <c r="D12" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>5.68238</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E12" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>7.86844</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>1.02279</v>
-      </c>
-      <c r="E12" s="8" t="n">
+      <c r="D13" s="13" t="n">
+        <v>1.01452</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>7.72198</v>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="F13" s="16" t="n">
+        <v>-25.0529</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>1.01344</v>
-      </c>
-      <c r="E13" s="8" t="n">
+      <c r="D14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>-26.5374</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D14" s="8" t="n">
+      <c r="E14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>-21.4964</v>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="16" t="n">
+        <v>-13.4529</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1394,7 +1413,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1445,518 +1464,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>31.838</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>-54.7681</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>63.34984626350722</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>434.3999387210523</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0.145833</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="D2" s="14" t="n">
+        <v>35.292</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>32.2569</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>47.81247600375869</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>434.3982338211499</v>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>0.110066</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>-203.999</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>-30.4383</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>206.2573201316501</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>434.3996969980626</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>0.47481</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="D3" s="14" t="n">
+        <v>-141.33</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>6.02293</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>141.4582786046292</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>434.4008064262046</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>-182.661</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-28.0685</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>184.8049826526601</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>434.3988102604209</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>0.4254270000000001</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="D4" s="14" t="n">
+        <v>-179.391</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>-26.7864</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>181.3798282774576</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>434.400042816053</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.417541</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>-213.589</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>-55.9921</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>220.8061959805703</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>868.7992413194135</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.254151</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="D5" s="14" t="n">
+        <v>-178.711</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>-55.4613</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>187.1191527307934</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>868.8022469114175</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>0.215376</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>63.9873</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-10.9719</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>64.92116104091177</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>434.4005422610356</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.14945</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="D6" s="14" t="n">
+        <v>61.8293</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>-4.28648</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>61.97770768010383</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>434.4008556576799</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>0.142674</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>51.8189</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>9.83418</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>52.74381000157648</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>434.3986064798999</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.121418</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="D7" s="14" t="n">
+        <v>87.90519999999999</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>-2.11211</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>87.93057031369749</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>434.4009441536695</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>0.202418</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>-355.092</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-86.062</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>365.3724076993226</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>868.8007259559494</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.420548</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="D8" s="14" t="n">
+        <v>-317.701</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>-41.4582</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>320.394612545592</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>868.8007759291281</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0.368778</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>299.985</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>158.083</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>339.0888307125435</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>434.4006850107528</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.78059</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="D9" s="19" t="n">
+        <v>393.367</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>149.662</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>420.8756478260533</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>434.399817339277</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>0.968867</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>1.0-8.0</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>-393.962</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>93.1521</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>404.825111842645</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1000.000276274057</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.404825</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>3.0-9.0</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>303.711</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>49.0718</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>307.6498221618859</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>999.9994219466469</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>1.0-8.0</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>-327.839</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>72.9327</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>335.853522611108</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1000.001556070983</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0.335853</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>1.0-10.0</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>-158.297</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>524.4596649972236</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>999.999361242466</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0.5244599999999999</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>2.0-11.0</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>232.337</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>551.3442496018255</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>1000.00045271523</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>0.5513439999999999</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>3.0-9.0</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>338.589</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>67.764</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>345.3034471548177</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>999.9983989609669</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.345304</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>3.0-12.0</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>237.054</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>310.1525413663412</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>1000.001745487184</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>0.310152</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1.0-10.0</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>-17.5972</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>500.3095656169688</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>999.9991317722387</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.50031</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>2.0-11.0</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>500</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>148.659</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>521.6315733168383</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>999.9991820226487</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0.521632</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>3.0-12.0</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>218.855</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>296.4751440255995</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1000.000485793404</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.296475</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>158.169</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>339.1422010912237</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>499.9995593168413</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0.678285</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="E15" s="14" t="n">
+        <v>149.798</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>335.3199081533931</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>499.9998630463336</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0.6706399999999999</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1980,12 +1999,12 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
@@ -2065,40 +2084,40 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>4.02456e-16</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>0.781049</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>1.199999995343813e-07</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>0.06895099999999998</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>5.0239387392e-15</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="B2" s="21" t="n">
+        <v>1.85528e-14</v>
+      </c>
+      <c r="C2" s="21" t="n">
+        <v>0.0821953</v>
+      </c>
+      <c r="D2" s="21" t="n">
+        <v>1.68485e-14</v>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>2e-16</v>
+      </c>
+      <c r="F2" s="22" t="n">
+        <v>0.6178047000000185</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>1.675952230246252e-14</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>9.2764e-12</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>3.8491240675e-12</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>2.4309e-14</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2110,40 +2129,40 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>5.3003e-18</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>3.4772e-17</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>1.07548</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>2.000000000062812e-06</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>0.07451999999999992</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>9.332185206999999e-16</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>8.693e-15</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="15" t="inlineStr">
+      <c r="B3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="21" t="n">
+        <v>2e-16</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>5.37698e-15</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>0.117002</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>8.897769753748434e-17</v>
+      </c>
+      <c r="G3" s="22" t="n">
+        <v>1.032998000000005</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>5.4088e-14</v>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>1.344245e-12</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2155,40 +2174,40 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>3.51477e-16</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>6.03546e-26</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>1.66601</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>2.799999999951083e-06</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.08399000000000001</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>6.800376996000004e-15</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>1.39209091992e-23</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
+      <c r="B4" s="21" t="n">
+        <v>13.4888</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>2e-16</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>1.39827e-14</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>0.11587</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>2e-16</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>1.634130000000014</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>5e-14</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>2.377059e-12</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2200,40 +2219,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>3.65336e-17</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>1.0873e-16</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1.41985</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>3.999999999856445e-06</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.08014999999999994</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>1.179962212800001e-15</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>1.63095e-14</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
+      <c r="B5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>2.00001e-16</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>0.0941442</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>2.00001e-16</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>1.4058558</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>3.570817854e-14</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2277,7 +2296,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>614.7682</v>
+        <v>698.98</v>
       </c>
     </row>
     <row r="4">
@@ -2287,7 +2306,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>121.545</v>
       </c>
     </row>
     <row r="5">
@@ -2317,7 +2336,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11.23180000000002</v>
+        <v>48.56499999999998</v>
       </c>
     </row>
     <row r="8">
@@ -2327,7 +2346,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1087.56</v>
+        <v>4779.62</v>
       </c>
     </row>
     <row r="9">
@@ -2337,7 +2356,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.76905748546135</v>
+        <v>6.647900057226243</v>
       </c>
     </row>
     <row r="10">
@@ -2347,7 +2366,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1.09309</v>
       </c>
     </row>
     <row r="11">
@@ -2357,7 +2376,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2367,7 +2386,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2386,7 +2405,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2398,7 +2417,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (78.1%)</t>
+          <t>6.0-&gt;7.0 (96.9%)</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2431,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
@@ -2470,15 +2489,15 @@
       <c r="C22" s="3" t="n">
         <v>0.85</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>0.719973</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
+      <c r="D22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>1.09309</v>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=ACTIVE</t>
         </is>
       </c>
     </row>
@@ -2494,13 +2513,13 @@
       <c r="C23" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>1.26786</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="D23" s="21" t="n">
+        <v>1.44088</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2518,13 +2537,13 @@
       <c r="C24" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D24" s="13" t="n">
-        <v>2.23035</v>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="D24" s="21" t="n">
+        <v>15.7888</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2542,13 +2561,13 @@
       <c r="C25" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D25" s="13" t="n">
-        <v>1.76311</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="D25" s="21" t="n">
+        <v>1.73562</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +66,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,20 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-        <bgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,23 +112,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,7 +492,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,7 +511,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infeasible</t>
+          <t>solved</t>
         </is>
       </c>
     </row>
@@ -541,7 +522,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4779.62</v>
+        <v>1471.37</v>
       </c>
     </row>
     <row r="5">
@@ -561,7 +542,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-76.2609600100258</v>
+        <v>28.3866853414994</v>
       </c>
     </row>
     <row r="7">
@@ -571,7 +552,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>698.98</v>
+        <v>621.4654</v>
       </c>
     </row>
     <row r="8">
@@ -581,7 +562,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>121.545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -611,7 +592,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>48.56499999999998</v>
+        <v>4.534599999999955</v>
       </c>
     </row>
     <row r="12">
@@ -621,7 +602,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6.647900057226243</v>
+        <v>2.367581262530786</v>
       </c>
     </row>
     <row r="13">
@@ -631,7 +612,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.09309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -641,7 +622,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -651,7 +632,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -681,7 +662,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>INVALID (solver did not converge)</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -708,9 +689,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -777,179 +758,179 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>1.09309</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>121.545</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>-121.545</v>
-      </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>ABSORPTION</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="n">
-        <v>132.85962405</v>
-      </c>
-      <c r="K2" s="11" t="n">
-        <v>118.086437025</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>14.77318702499998</v>
+      <c r="D2" s="8" t="n">
+        <v>0.771858</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>44.9114</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>44.9114</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>34.6652233812</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>33.051607079968</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>1.613616301232</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>1.44088</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <v>270.44</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="14" t="n">
-        <v>270.44</v>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="D3" s="8" t="n">
+        <v>2.51122</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>142.245</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>142.245</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="15" t="n">
-        <v>389.6715872</v>
-      </c>
-      <c r="K3" s="15" t="n">
-        <v>316.5337936</v>
-      </c>
-      <c r="L3" s="15" t="n">
-        <v>73.13779359999995</v>
+      <c r="J3" s="10" t="n">
+        <v>357.2084889</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>306.6251000625</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>50.58338883749997</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>15.7888</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="D4" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="14" t="n">
+      <c r="G4" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>3947.2</v>
-      </c>
-      <c r="K4" s="15" t="n">
+      <c r="J4" s="10" t="n">
+        <v>575</v>
+      </c>
+      <c r="K4" s="10" t="n">
         <v>462.5</v>
       </c>
-      <c r="L4" s="15" t="n">
-        <v>3484.7</v>
+      <c r="L4" s="10" t="n">
+        <v>112.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="13" t="n">
-        <v>1.73562</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>178.54</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>178.54</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="D5" s="8" t="n">
+        <v>2.73723</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>184.309</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>184.309</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>309.8775948</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>262.0627974</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>47.81479740000003</v>
+      <c r="J5" s="10" t="n">
+        <v>504.49612407</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>436.557614962</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>67.93850910799995</v>
       </c>
     </row>
   </sheetData>
@@ -1014,377 +995,377 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="13" t="n">
-        <v>0.986374</v>
-      </c>
-      <c r="E2" s="13" t="n">
+      <c r="D2" s="8" t="n">
+        <v>1.03885</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>2.97628</v>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="n">
+        <v>2.26334</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="13" t="n">
-        <v>1.0184</v>
-      </c>
-      <c r="E3" s="13" t="n">
+      <c r="D3" s="8" t="n">
+        <v>0.967081</v>
+      </c>
+      <c r="E3" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="16" t="n">
-        <v>4.38349</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="F3" s="11" t="n">
+        <v>4.66555</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="13" t="n">
-        <v>0.982815</v>
-      </c>
-      <c r="E4" s="13" t="n">
+      <c r="D4" s="8" t="n">
+        <v>0.999068</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="16" t="n">
-        <v>-26.5471</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="F4" s="11" t="n">
+        <v>-28.0643</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="8" t="n">
+        <v>0.960389</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>-33.1529</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="D6" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="16" t="n">
-        <v>-30.8306</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="n">
+      <c r="F6" s="11" t="n">
+        <v>-23.3605</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="13" t="n">
-        <v>0.978776</v>
-      </c>
-      <c r="E6" s="13" t="n">
+      <c r="D7" s="8" t="n">
+        <v>1.00694</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="16" t="n">
-        <v>-21.2808</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n">
+      <c r="F7" s="11" t="n">
+        <v>-25.7233</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>1.00835</v>
-      </c>
-      <c r="E7" s="13" t="n">
+      <c r="D8" s="8" t="n">
+        <v>1.00711</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>-17.6941</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="F8" s="11" t="n">
+        <v>-25.7106</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="13" t="n">
-        <v>1.00853</v>
-      </c>
-      <c r="E8" s="13" t="n">
+      <c r="D9" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="16" t="n">
-        <v>-17.677</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="n">
+      <c r="E9" s="8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="13" t="n">
+      <c r="D10" s="8" t="n">
+        <v>1.00789</v>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="n">
+      <c r="F10" s="11" t="n">
+        <v>-25.526</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>0.990121</v>
-      </c>
-      <c r="E10" s="13" t="n">
+      <c r="D11" s="8" t="n">
+        <v>1.04258</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="16" t="n">
-        <v>-24.2218</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="n">
+      <c r="F11" s="11" t="n">
+        <v>5.70393</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="13" t="n">
-        <v>0.967757</v>
-      </c>
-      <c r="E11" s="13" t="n">
+      <c r="D12" s="8" t="n">
+        <v>0.983621</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="16" t="n">
-        <v>6.88077</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="F12" s="11" t="n">
+        <v>8.583729999999999</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D13" s="8" t="n">
+        <v>1.03029</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="F13" s="11" t="n">
+        <v>-26.6169</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="16" t="n">
-        <v>7.86844</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>1.01452</v>
-      </c>
-      <c r="E13" s="13" t="n">
+      <c r="E14" s="8" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>-25.0529</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>-13.4529</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="F14" s="11" t="n">
+        <v>-21.4805</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1413,7 +1394,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1464,518 +1445,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
-        <v>35.292</v>
-      </c>
-      <c r="E2" s="14" t="n">
-        <v>32.2569</v>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>47.81247600375869</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>434.3982338211499</v>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>0.110066</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="D2" s="9" t="n">
+        <v>35.2079</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>-97.5213</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>103.6822076158682</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>434.4002095528648</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0.238679</v>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>-141.33</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>6.02293</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <v>141.4582786046292</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>434.4008064262046</v>
-      </c>
-      <c r="H3" s="17" t="n">
-        <v>0.32564</v>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="D3" s="9" t="n">
+        <v>-203.837</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>-29.5834</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>205.9725712918106</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>434.3992392610235</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0.474155</v>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>-179.391</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>-26.7864</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>181.3798282774576</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>434.400042816053</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.417541</v>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="D4" s="9" t="n">
+        <v>-178.448</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>-21.0897</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>179.6899110971175</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>434.399798615542</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0.413651</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>-178.711</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>-55.4613</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>187.1191527307934</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>868.8022469114175</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>0.215376</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="D5" s="9" t="n">
+        <v>-218.045</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>-67.4106</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>228.2275421971678</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>868.7994815132789</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.262693</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>61.8293</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>-4.28648</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>61.97770768010383</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>434.4008556576799</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>0.142674</v>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="D6" s="9" t="n">
+        <v>59.7457</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-19.2352</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>62.76576764072912</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>434.4012488284779</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.144488</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>87.90519999999999</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>-2.11211</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>87.93057031369749</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>434.4009441536695</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0.202418</v>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="D7" s="9" t="n">
+        <v>51.7299</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>6.34357</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>52.11740049498727</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>434.398550501661</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.119976</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>-317.701</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>-41.4582</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>320.394612545592</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>868.8007759291281</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>0.368778</v>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="D8" s="9" t="n">
+        <v>-359.757</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-75.96850000000001</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>367.6905112200341</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>868.7990114292055</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.423217</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="19" t="n">
-        <v>393.367</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>149.662</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>420.8756478260533</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>434.399817339277</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0.968867</v>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>WARNING</t>
+      <c r="D9" s="9" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>154.994</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>337.6642417194927</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>434.3998828263204</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.777312</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>-393.962</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>93.1521</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>404.825111842645</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>1000.000276274057</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.404825</v>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="D10" s="9" t="n">
+        <v>-331.371</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>82.5338</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>341.4946087179708</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>1000.001782514395</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.341494</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>303.711</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>49.0718</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>307.6498221618859</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>999.9994219466469</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>0.30765</v>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="D11" s="9" t="n">
+        <v>343.045</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>60.1828</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>348.2841389452583</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>1000.00039894241</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.348284</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>-158.297</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>524.4596649972236</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>999.999361242466</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>0.5244599999999999</v>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="E12" s="9" t="n">
+        <v>14.7707</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>500.2181259995384</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>1000.000251889253</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.5002179999999999</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>232.337</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>551.3442496018255</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>1000.00045271523</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>0.5513439999999999</v>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="E13" s="9" t="n">
+        <v>105.935</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>511.099035633017</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>1000.000069718424</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.5110990000000001</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="14" t="n">
-        <v>237.054</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>310.1525413663412</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>1000.001745487184</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>0.310152</v>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="E14" s="9" t="n">
+        <v>237.447</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>310.4530202929261</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1000.000065365534</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.310453</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="9" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="14" t="n">
-        <v>149.798</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>335.3199081533931</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>499.9998630463336</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0.6706399999999999</v>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="E15" s="9" t="n">
+        <v>155.073</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>337.7093947893662</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>499.9998442290877</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.675419</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2000,12 +1981,12 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -2084,40 +2065,40 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n">
-        <v>1.85528e-14</v>
-      </c>
-      <c r="C2" s="21" t="n">
-        <v>0.0821953</v>
-      </c>
-      <c r="D2" s="21" t="n">
-        <v>1.68485e-14</v>
-      </c>
-      <c r="E2" s="21" t="n">
-        <v>2e-16</v>
-      </c>
-      <c r="F2" s="22" t="n">
-        <v>0.6178047000000185</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>1.675952230246252e-14</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>9.2764e-12</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>3.8491240675e-12</v>
-      </c>
-      <c r="K2" s="13" t="n">
-        <v>2.4309e-14</v>
-      </c>
-      <c r="L2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="B2" s="13" t="n">
+        <v>3.04873e-08</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>2.84456e-08</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>3.02353e-08</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>1.81159</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>2.420416998736746e-07</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>0.0384100302353001</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>1.387442267478e-05</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>1.27753171984e-06</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>1.0582355e-05</v>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2129,40 +2110,40 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="21" t="n">
-        <v>2e-16</v>
-      </c>
-      <c r="D3" s="21" t="n">
-        <v>5.37698e-15</v>
-      </c>
-      <c r="E3" s="21" t="n">
-        <v>0.117002</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>8.897769753748434e-17</v>
-      </c>
-      <c r="G3" s="22" t="n">
-        <v>1.032998000000005</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>5.4088e-14</v>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>1.344245e-12</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="n">
+        <v>2.83991e-08</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>1.81572e-08</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>3.01845e-08</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>0.835103</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>5.010241900254801e-06</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0.3148970301844999</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>6.1840460205e-06</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>2.582770914e-06</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>7.546125000000001e-06</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2174,40 +2155,40 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n">
-        <v>13.4888</v>
-      </c>
-      <c r="C4" s="21" t="n">
-        <v>2e-16</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>1.39827e-14</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>0.11587</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>2e-16</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>1.634130000000014</v>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>5e-14</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>2.377059e-12</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>3.01895e-08</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1.48329</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.2667100301895</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>5.132215e-06</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2219,40 +2200,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>2.00001e-16</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>0.0941442</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>2.00001e-16</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>1.4058558</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>3.570817854e-14</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="n">
+        <v>2.69658e-08</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>1.20441e-08</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>3.01377e-08</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1.15111</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>6.014921700172534e-06</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>0.3488900301376998</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>9.624363678000008e-07</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2.2198360269e-06</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>4.520655e-06</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2296,7 +2277,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>698.98</v>
+        <v>621.4654</v>
       </c>
     </row>
     <row r="4">
@@ -2306,7 +2287,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>121.545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2336,7 +2317,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>48.56499999999998</v>
+        <v>4.534599999999955</v>
       </c>
     </row>
     <row r="8">
@@ -2346,7 +2327,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>4779.62</v>
+        <v>1471.37</v>
       </c>
     </row>
     <row r="9">
@@ -2356,7 +2337,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6.647900057226243</v>
+        <v>2.367581262530786</v>
       </c>
     </row>
     <row r="10">
@@ -2366,7 +2347,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.09309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2376,7 +2357,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2386,7 +2367,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2405,7 +2386,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="21" t="n">
+      <c r="B14" s="13" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2417,7 +2398,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (96.9%)</t>
+          <t>6.0-&gt;7.0 (77.7%)</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2412,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
@@ -2487,17 +2468,17 @@
         <v>0.7</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>1.09309</v>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=ACTIVE</t>
+        <v>1.85</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>0.771858</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=DB</t>
         </is>
       </c>
     </row>
@@ -2508,18 +2489,18 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D23" s="21" t="n">
-        <v>1.44088</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="D23" s="13" t="n">
+        <v>2.51122</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2537,13 +2518,13 @@
       <c r="C24" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D24" s="21" t="n">
-        <v>15.7888</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
+      <c r="D24" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2556,18 +2537,18 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D25" s="21" t="n">
-        <v>1.73562</v>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="D25" s="13" t="n">
+        <v>2.73723</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,8 +78,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00BDD7EE"/>
+        <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -101,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,16 +118,20 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,7 +502,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,7 +532,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1471.37</v>
+        <v>1781.21</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +552,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.3866853414994</v>
+        <v>28.0972799468967</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +562,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>621.4654</v>
+        <v>659.542</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +572,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0</v>
+        <v>25.0106</v>
       </c>
     </row>
     <row r="9">
@@ -592,7 +602,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4.534599999999955</v>
+        <v>-8.531399999999916</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +612,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.367581262530786</v>
+        <v>2.627104269204994</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +622,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>1.94004</v>
       </c>
     </row>
     <row r="14">
@@ -622,7 +632,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -632,7 +642,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -689,9 +699,9 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -758,47 +768,47 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0.771858</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>44.9114</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>44.9114</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>34.6652233812</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>33.051607079968</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>1.613616301232</v>
+      <c r="D2" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>1.94004</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>25.0106</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>-25.0106</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>ABSORPTION</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>48.521564424</v>
+      </c>
+      <c r="K2" s="11" t="n">
+        <v>47.395564202248</v>
+      </c>
+      <c r="L2" s="11" t="n">
+        <v>1.126000221751994</v>
       </c>
     </row>
     <row r="3">
@@ -815,34 +825,34 @@
       <c r="C3" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>2.51122</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>142.245</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>142.245</v>
+      <c r="D3" s="12" t="n">
+        <v>2.86276</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>212.552</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>212.552</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="10" t="n">
-        <v>357.2084889</v>
-      </c>
-      <c r="K3" s="10" t="n">
-        <v>306.6251000625</v>
-      </c>
-      <c r="L3" s="10" t="n">
-        <v>50.58338883749997</v>
+      <c r="J3" s="14" t="n">
+        <v>608.48536352</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>495.5394817599999</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>112.94588176</v>
       </c>
     </row>
     <row r="4">
@@ -859,19 +869,19 @@
       <c r="C4" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="12" t="n">
         <v>2.3</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="E4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9" t="n">
+      <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="n">
         <v>250</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -879,13 +889,13 @@
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="14" t="n">
         <v>575</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="14" t="n">
         <v>462.5</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="14" t="n">
         <v>112.5</v>
       </c>
     </row>
@@ -903,34 +913,34 @@
       <c r="C5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>2.73723</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>184.309</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>184.309</v>
+      <c r="D5" s="12" t="n">
+        <v>2.78796</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>196.99</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n">
-        <v>504.49612407</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>436.557614962</v>
-      </c>
-      <c r="L5" s="10" t="n">
-        <v>67.93850910799995</v>
+      <c r="J5" s="14" t="n">
+        <v>549.2002404</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>471.5901202</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>77.61012019999998</v>
       </c>
     </row>
   </sheetData>
@@ -1005,17 +1015,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>1.03885</v>
-      </c>
-      <c r="E2" s="8" t="n">
+      <c r="D2" s="12" t="n">
+        <v>1.01909</v>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="11" t="n">
-        <v>2.26334</v>
+      <c r="F2" s="15" t="n">
+        <v>2.31982</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -1034,17 +1044,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>0.967081</v>
-      </c>
-      <c r="E3" s="8" t="n">
+      <c r="D3" s="12" t="n">
+        <v>1.00198</v>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="11" t="n">
-        <v>4.66555</v>
+      <c r="F3" s="15" t="n">
+        <v>3.92947</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
@@ -1063,17 +1073,17 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>0.999068</v>
-      </c>
-      <c r="E4" s="8" t="n">
+      <c r="D4" s="12" t="n">
+        <v>0.9848170000000001</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>-28.0643</v>
+      <c r="F4" s="15" t="n">
+        <v>-28.7024</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
@@ -1092,17 +1102,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>0.960389</v>
-      </c>
-      <c r="E5" s="8" t="n">
+      <c r="D5" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="11" t="n">
-        <v>-33.1529</v>
+      <c r="F5" s="15" t="n">
+        <v>-33.8361</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
@@ -1121,17 +1131,17 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E6" s="8" t="n">
+      <c r="D6" s="12" t="n">
+        <v>0.9628409999999999</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>-23.3605</v>
+      <c r="F6" s="15" t="n">
+        <v>-23.3898</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
@@ -1150,17 +1160,17 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>1.00694</v>
-      </c>
-      <c r="E7" s="8" t="n">
+      <c r="D7" s="12" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>-25.7233</v>
+      <c r="F7" s="15" t="n">
+        <v>-26.4708</v>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
@@ -1179,17 +1189,17 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>1.00711</v>
-      </c>
-      <c r="E8" s="8" t="n">
+      <c r="D8" s="12" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="11" t="n">
-        <v>-25.7106</v>
+      <c r="F8" s="15" t="n">
+        <v>-26.4581</v>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
@@ -1208,16 +1218,16 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E9" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1237,17 +1247,17 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>1.00789</v>
-      </c>
-      <c r="E10" s="8" t="n">
+      <c r="D10" s="12" t="n">
+        <v>0.992563</v>
+      </c>
+      <c r="E10" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>-25.526</v>
+      <c r="F10" s="15" t="n">
+        <v>-26.1255</v>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -1266,17 +1276,17 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>1.04258</v>
-      </c>
-      <c r="E11" s="8" t="n">
+      <c r="D11" s="12" t="n">
+        <v>1.01387</v>
+      </c>
+      <c r="E11" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>5.70393</v>
+      <c r="F11" s="15" t="n">
+        <v>5.92667</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -1295,17 +1305,17 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>0.983621</v>
-      </c>
-      <c r="E12" s="8" t="n">
+      <c r="D12" s="12" t="n">
+        <v>1.02689</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="11" t="n">
-        <v>8.583729999999999</v>
+      <c r="F12" s="15" t="n">
+        <v>7.55141</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -1324,17 +1334,17 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>1.03029</v>
-      </c>
-      <c r="E13" s="8" t="n">
+      <c r="D13" s="12" t="n">
+        <v>1.01646</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>-26.6169</v>
+      <c r="F13" s="15" t="n">
+        <v>-27.214</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -1353,17 +1363,17 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="12" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="12" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>-21.4805</v>
+      <c r="F14" s="15" t="n">
+        <v>-22.2148</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
@@ -1460,20 +1470,20 @@
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>35.2079</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>-97.5213</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>103.6822076158682</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>434.4002095528648</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0.238679</v>
+      <c r="D2" s="13" t="n">
+        <v>30.5008</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>-26.6978</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>40.53481621371929</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>434.3999628528669</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <v>0.0933122</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -1497,20 +1507,20 @@
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>-203.837</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>-29.5834</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>205.9725712918106</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>434.3992392610235</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>0.474155</v>
+      <c r="D3" s="13" t="n">
+        <v>-203.673</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>-24.1611</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>205.1010718699686</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>434.4008791117355</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>0.472147</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -1534,20 +1544,20 @@
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>-178.448</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>-21.0897</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>179.6899110971175</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>434.399798615542</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>0.413651</v>
+      <c r="D4" s="13" t="n">
+        <v>-184.286</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>-29.2815</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>186.5977921580264</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>434.4009390202498</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>0.429552</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -1571,20 +1581,20 @@
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>-218.045</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>-67.4106</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>228.2275421971678</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>868.7994815132789</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.262693</v>
+      <c r="D5" s="13" t="n">
+        <v>-213.058</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>-57.5675</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>220.6982746200115</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>868.7984923650299</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>0.254027</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -1608,20 +1618,20 @@
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>59.7457</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-19.2352</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>62.76576764072912</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>434.4012488284779</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.144488</v>
+      <c r="D6" s="13" t="n">
+        <v>65.2741</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>-11.9104</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>66.35183312441337</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>434.39894938206</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.152744</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -1645,20 +1655,20 @@
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>51.7299</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>6.34357</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>52.11740049498727</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>434.398550501661</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.119976</v>
+      <c r="D7" s="13" t="n">
+        <v>51.0558</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>9.150499999999999</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>51.86932006388747</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>434.401863119221</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.119404</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -1682,20 +1692,20 @@
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>-359.757</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>-75.96850000000001</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>367.6905112200341</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>868.7990114292055</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.423217</v>
+      <c r="D8" s="13" t="n">
+        <v>-354.926</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>-73.0012</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>362.3556825516056</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>868.8001288772446</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.417076</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -1719,20 +1729,20 @@
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>299.99</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>154.994</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>337.6642417194927</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>434.3998828263204</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.777312</v>
+      <c r="D9" s="13" t="n">
+        <v>299.984</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>166.525</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>343.1049050669488</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>434.3996357057834</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.789837</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -1756,20 +1766,20 @@
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>-331.371</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>82.5338</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>341.4946087179708</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>1000.001782514395</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0.341494</v>
+      <c r="D10" s="13" t="n">
+        <v>-326.828</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>78.8883</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>336.2140768333325</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1000.000228525084</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>0.336214</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -1793,20 +1803,20 @@
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>343.045</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>60.1828</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>348.2841389452583</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>1000.00039894241</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.348284</v>
+      <c r="D11" s="13" t="n">
+        <v>338.058</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>51.0741</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>341.8943916691381</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1000.001145586463</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.341894</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -1830,20 +1840,20 @@
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="9" t="n">
-        <v>14.7707</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>500.2181259995384</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>1000.000251889253</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.5002179999999999</v>
+      <c r="E12" s="13" t="n">
+        <v>-56.7067</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>503.2053753934769</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1000.000746005061</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0.503205</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1867,20 +1877,20 @@
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>105.935</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>511.099035633017</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>1000.000069718424</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0.5110990000000001</v>
+      <c r="E13" s="13" t="n">
+        <v>176.162</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>530.1255042383831</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>999.9990648230479</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0.530126</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -1904,20 +1914,20 @@
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="9" t="n">
-        <v>237.447</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>310.4530202929261</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>1000.000065365534</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.310453</v>
+      <c r="E14" s="13" t="n">
+        <v>237.103</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>310.1899943728037</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>999.9999818588727</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>0.31019</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1941,20 +1951,20 @@
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>155.073</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>337.7093947893662</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>499.9998442290877</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>0.675419</v>
+      <c r="E15" s="13" t="n">
+        <v>166.614</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>343.1620972601724</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>499.9994131937091</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <v>0.686325</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1978,15 +1988,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
@@ -2065,42 +2075,42 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>3.04873e-08</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>2.84456e-08</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>3.02353e-08</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>1.81159</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>2.420416998736746e-07</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>0.0384100302353001</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>1.387442267478e-05</v>
-      </c>
-      <c r="I2" s="8" t="n">
-        <v>1.27753171984e-06</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>1.0582355e-05</v>
-      </c>
-      <c r="K2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B2" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>0.699622</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1.5533e-16</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>2.22044e-16</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>0.0003779999999999895</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>1.839999999986398e-06</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>5.0480603502e-14</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>5.5534536664e-15</v>
+      </c>
+      <c r="L2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="19" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2110,42 +2120,42 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
-        <v>2.83991e-08</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>1.81572e-08</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>3.01845e-08</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>0.835103</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>5.010241900254801e-06</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>0.3148970301844999</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>6.1840460205e-06</v>
-      </c>
-      <c r="I3" s="8" t="n">
-        <v>2.582770914e-06</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>7.546125000000001e-06</v>
-      </c>
-      <c r="K3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>1.14962</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
+      <c r="G3" s="18" t="n">
+        <v>0.0003799999999998249</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2155,42 +2165,42 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>3.01895e-08</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>1.48329</v>
-      </c>
-      <c r="F4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.2667100301895</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>5.132215e-06</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B4" s="17" t="n">
+        <v>1.9154e-08</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>3.07421e-26</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>1.15783e-17</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>1.74962</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>1.9154e-08</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>0.000380000000000047</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>7.685525000000001e-24</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>1.968311e-15</v>
+      </c>
+      <c r="K4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2200,42 +2210,42 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>2.69658e-08</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>1.20441e-08</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>3.01377e-08</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1.15111</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>6.014921700172534e-06</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.3488900301376998</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>9.624363678000008e-07</v>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>2.2198360269e-06</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>4.520655e-06</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="B5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>1.49962</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.000380000000000047</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2287,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>621.4654</v>
+        <v>659.542</v>
       </c>
     </row>
     <row r="4">
@@ -2287,7 +2297,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>25.0106</v>
       </c>
     </row>
     <row r="5">
@@ -2317,7 +2327,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.534599999999955</v>
+        <v>-8.531399999999916</v>
       </c>
     </row>
     <row r="8">
@@ -2327,7 +2337,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1471.37</v>
+        <v>1781.21</v>
       </c>
     </row>
     <row r="9">
@@ -2337,7 +2347,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2.367581262530786</v>
+        <v>2.627104269204994</v>
       </c>
     </row>
     <row r="10">
@@ -2347,7 +2357,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1.94004</v>
       </c>
     </row>
     <row r="11">
@@ -2357,7 +2367,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2367,7 +2377,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -2386,7 +2396,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="17" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2398,7 +2408,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (77.7%)</t>
+          <t>6.0-&gt;7.0 (79.0%)</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2422,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
@@ -2470,15 +2480,15 @@
       <c r="C22" s="3" t="n">
         <v>1.85</v>
       </c>
-      <c r="D22" s="13" t="n">
-        <v>0.771858</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>1.94004</v>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>INJ=DB / ABS=ACTIVE</t>
         </is>
       </c>
     </row>
@@ -2494,13 +2504,13 @@
       <c r="C23" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="D23" s="13" t="n">
-        <v>2.51122</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="D23" s="17" t="n">
+        <v>2.86276</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2518,13 +2528,13 @@
       <c r="C24" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="17" t="n">
         <v>2.3</v>
       </c>
-      <c r="E24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2542,13 +2552,13 @@
       <c r="C25" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="D25" s="13" t="n">
-        <v>2.73723</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="D25" s="17" t="n">
+        <v>2.78796</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branch Flows" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KKT Verification" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Statistics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voltage Profile" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,9 @@
       <sz val="12"/>
     </font>
     <font>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -57,7 +61,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,8 +70,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,6 +84,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
         <bgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,23 +125,26 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -206,6 +219,195 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Voltage Profile</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Voltage Profile'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Voltage Profile'!$A$2:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage Profile'!$B$2:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Voltage Profile'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Voltage Profile'!$A$2:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage Profile'!$C$2:$C$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Voltage Profile'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Voltage Profile'!$A$2:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Voltage Profile'!$D$2:$D$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Bus</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.07"/>
+          <min val="0.93"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>V (pu)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9000000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,10 +700,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -532,7 +734,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1781.21</v>
+        <v>1760.45</v>
       </c>
     </row>
     <row r="5">
@@ -548,11 +750,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Reference Bus P_ref (MW)</t>
+          <t>P_ref Bus 8 (MW)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.0972799468967</v>
+        <v>28.0972813272805</v>
       </c>
     </row>
     <row r="7">
@@ -582,7 +784,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10">
@@ -592,7 +794,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1046</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11">
@@ -602,7 +804,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-8.531399999999916</v>
+        <v>-170.5313999999999</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +824,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.94004</v>
+        <v>1.11003</v>
       </c>
     </row>
     <row r="14">
@@ -672,7 +874,28 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Gen 0 ABS stationarity FAIL: lam=1.1100, expected=-0.0000, residual=1.1100e+00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Gen 1 INJ stationarity FAIL: lam=2.8628, expected=0.0000, residual=2.8628e+00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Gen 2 INJ stationarity FAIL: lam=2.3000, expected=0.0000, residual=2.3000e+00</t>
         </is>
       </c>
     </row>
@@ -700,246 +923,246 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>λ_inj (€/MVAr)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>λ_abs (€/MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Q_inj (MVAr)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Q_abs (MVAr)</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Q_net (MVAr)</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>revenue (€)</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>cost (€)</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>profit (€)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="n">
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>G0.0</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>1.94004</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10" t="n">
+      <c r="D2" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1.11003</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>25.0106</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>-25.0106</v>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>ABSORPTION</t>
         </is>
       </c>
-      <c r="J2" s="11" t="n">
-        <v>48.521564424</v>
-      </c>
-      <c r="K2" s="11" t="n">
-        <v>47.395564202248</v>
-      </c>
-      <c r="L2" s="11" t="n">
-        <v>1.126000221751994</v>
+      <c r="J2" s="12" t="n">
+        <v>27.762516318</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="n">
+        <v>27.762516318</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n">
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>G1.0</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="14" t="n">
         <v>2.86276</v>
       </c>
-      <c r="E3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13" t="n">
+      <c r="E3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="n">
         <v>212.552</v>
       </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13" t="n">
+      <c r="G3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15" t="n">
         <v>212.552</v>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J3" s="16" t="n">
         <v>608.48536352</v>
       </c>
-      <c r="K3" s="14" t="n">
-        <v>495.5394817599999</v>
-      </c>
-      <c r="L3" s="14" t="n">
-        <v>112.94588176</v>
+      <c r="K3" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="16" t="n">
+        <v>608.48536352</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>G2.0</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="14" t="n">
         <v>2.3</v>
       </c>
-      <c r="E4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13" t="n">
+      <c r="E4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13" t="n">
+      <c r="G4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="J4" s="16" t="n">
         <v>575</v>
       </c>
-      <c r="K4" s="14" t="n">
-        <v>462.5</v>
-      </c>
-      <c r="L4" s="14" t="n">
-        <v>112.5</v>
+      <c r="K4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>575</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>G3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="14" t="n">
         <v>2.78796</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>196.99</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13" t="n">
+      <c r="G5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="15" t="n">
         <v>196.99</v>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" s="16" t="n">
         <v>549.2002404</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="16" t="n">
         <v>471.5901202</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L5" s="16" t="n">
         <v>77.61012019999998</v>
       </c>
     </row>
@@ -968,414 +1191,414 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>V_min</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>V_pu</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>V_max</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>θ (deg)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="14" t="n">
         <v>1.01909</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="17" t="n">
         <v>2.31982</v>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="14" t="n">
         <v>1.00198</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="17" t="n">
         <v>3.92947</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="14" t="n">
         <v>0.9848170000000001</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="17" t="n">
         <v>-28.7024</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="17" t="n">
         <v>-33.8361</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="14" t="n">
         <v>0.9628409999999999</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="17" t="n">
         <v>-23.3898</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="14" t="n">
         <v>1.0038</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="17" t="n">
         <v>-26.4708</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="14" t="n">
         <v>1.00397</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="17" t="n">
         <v>-26.4581</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="14" t="n">
         <v>1.03</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="F9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="14" t="n">
         <v>0.992563</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="17" t="n">
         <v>-26.1255</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="14" t="n">
         <v>1.01387</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="17" t="n">
         <v>5.92667</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="14" t="n">
         <v>1.02689</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="17" t="n">
         <v>7.55141</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="14" t="n">
         <v>1.01646</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="17" t="n">
         <v>-27.214</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="17" t="n">
         <v>-22.2148</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1408,565 +1631,565 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>from_bus</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>to_bus</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>P_flow (MW)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Q_flow (MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>|S_flow| (MVA)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>S_max (MVA)</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>loading (%)</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="15" t="n">
         <v>30.5008</v>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="E2" s="15" t="n">
         <v>-26.6978</v>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="15" t="n">
         <v>40.53481621371929</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="15" t="n">
         <v>434.3999628528669</v>
       </c>
-      <c r="H2" s="16" t="n">
+      <c r="H2" s="18" t="n">
         <v>0.0933122</v>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="15" t="n">
         <v>-203.673</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="15" t="n">
         <v>-24.1611</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="15" t="n">
         <v>205.1010718699686</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="15" t="n">
         <v>434.4008791117355</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="18" t="n">
         <v>0.472147</v>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="15" t="n">
         <v>-184.286</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="15" t="n">
         <v>-29.2815</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="15" t="n">
         <v>186.5977921580264</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="15" t="n">
         <v>434.4009390202498</v>
       </c>
-      <c r="H4" s="16" t="n">
+      <c r="H4" s="18" t="n">
         <v>0.429552</v>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="15" t="n">
         <v>-213.058</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="15" t="n">
         <v>-57.5675</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="15" t="n">
         <v>220.6982746200115</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="15" t="n">
         <v>868.7984923650299</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="18" t="n">
         <v>0.254027</v>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="15" t="n">
         <v>65.2741</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="15" t="n">
         <v>-11.9104</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="15" t="n">
         <v>66.35183312441337</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="15" t="n">
         <v>434.39894938206</v>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="18" t="n">
         <v>0.152744</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
-        <v>51.0558</v>
-      </c>
-      <c r="E7" s="13" t="n">
+      <c r="D7" s="15" t="n">
+        <v>51.0557</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>9.150499999999999</v>
       </c>
-      <c r="F7" s="13" t="n">
-        <v>51.86932006388747</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>434.401863119221</v>
-      </c>
-      <c r="H7" s="16" t="n">
+      <c r="F7" s="15" t="n">
+        <v>51.86922163229366</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>434.4010387616299</v>
+      </c>
+      <c r="H7" s="18" t="n">
         <v>0.119404</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="15" t="n">
         <v>-354.926</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="15" t="n">
         <v>-73.0012</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="15" t="n">
         <v>362.3556825516056</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="15" t="n">
         <v>868.8001288772446</v>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="18" t="n">
         <v>0.417076</v>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="15" t="n">
         <v>299.984</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="15" t="n">
         <v>166.525</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="15" t="n">
         <v>343.1049050669488</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="15" t="n">
         <v>434.3996357057834</v>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="18" t="n">
         <v>0.789837</v>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>1.0-8.0</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="15" t="n">
         <v>-326.828</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="15" t="n">
         <v>78.8883</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="15" t="n">
         <v>336.2140768333325</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="15" t="n">
         <v>1000.000228525084</v>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="18" t="n">
         <v>0.336214</v>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>3.0-9.0</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="15" t="n">
         <v>338.058</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="15" t="n">
         <v>51.0741</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="15" t="n">
         <v>341.8943916691381</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="15" t="n">
         <v>1000.001145586463</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="18" t="n">
         <v>0.341894</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="15" t="n">
         <v>-56.7067</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="15" t="n">
         <v>503.2053753934769</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="15" t="n">
         <v>1000.000746005061</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="18" t="n">
         <v>0.503205</v>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="15" t="n">
         <v>176.162</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="15" t="n">
         <v>530.1255042383831</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="15" t="n">
         <v>999.9990648230479</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="18" t="n">
         <v>0.530126</v>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="15" t="n">
         <v>237.103</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="15" t="n">
         <v>310.1899943728037</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="15" t="n">
         <v>999.9999818588727</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="18" t="n">
         <v>0.31019</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="15" t="n">
         <v>166.614</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="15" t="n">
         <v>343.1620972601724</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="15" t="n">
         <v>499.9994131937091</v>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="18" t="n">
         <v>0.686325</v>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1988,14 +2211,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
@@ -2003,67 +2226,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>μ_qp_ub</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>μ_qp_lb</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>μ_qn_ub</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>μ_qn_lb</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>stat_inj_residual</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>stat_abs_residual</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>compl_qp_ub_violation</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>compl_qp_lb_violation</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>compl_qn_ub_violation</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>compl_qn_lb_violation</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>exclusivity_violation</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>overall_status</t>
         </is>
@@ -2075,42 +2298,42 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>0.699622</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>1.5533e-16</v>
-      </c>
-      <c r="E2" s="17" t="n">
-        <v>2.22044e-16</v>
-      </c>
-      <c r="F2" s="18" t="n">
-        <v>0.0003779999999999895</v>
-      </c>
-      <c r="G2" s="12" t="n">
-        <v>1.839999999986398e-06</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>5.0480603502e-14</v>
-      </c>
-      <c r="K2" s="12" t="n">
-        <v>5.5534536664e-15</v>
-      </c>
-      <c r="L2" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="19" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B2" s="19" t="n">
+        <v>3.38588e-16</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>0.699613</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>2.22045e-16</v>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>0.6996129999999997</v>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>1.11003</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>5.553478677e-15</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2120,42 +2343,42 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="17" t="n">
-        <v>1.14962</v>
-      </c>
-      <c r="F3" s="12" t="n">
-        <v>2.220446049250313e-16</v>
-      </c>
-      <c r="G3" s="18" t="n">
-        <v>0.0003799999999998249</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="19" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B3" s="19" t="n">
+        <v>1.01095e-16</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>4.5265e-22</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>2.69961</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>2.86276</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>2.69961</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>2.148794444e-14</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>9.621166279999999e-20</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2165,42 +2388,42 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
-        <v>1.9154e-08</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>3.07421e-26</v>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>1.15783e-17</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>1.74962</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>1.9154e-08</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>0.000380000000000047</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="12" t="n">
-        <v>7.685525000000001e-24</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>1.968311e-15</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="19" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="B4" s="19" t="n">
+        <v>1.74705e-08</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>2.96811e-26</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>2.09961</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>2.2999999825295</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>2.09961</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>4.367625e-06</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>7.420275e-24</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2210,40 +2433,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>1.49962</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.000380000000000047</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="B5" s="19" t="n">
+        <v>7.64796e-17</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>1.02754e-21</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>6.13047e-17</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>2.99961</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>7.647857245999999e-17</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0.0003899999999998904</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>1.759795596000001e-15</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>2.024151046e-19</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>9.195705e-15</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
@@ -2307,7 +2530,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>420</v>
+        <v>680</v>
       </c>
     </row>
     <row r="6">
@@ -2317,7 +2540,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1046</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="7">
@@ -2327,7 +2550,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-8.531399999999916</v>
+        <v>-170.5313999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2337,7 +2560,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1781.21</v>
+        <v>1760.45</v>
       </c>
     </row>
     <row r="9">
@@ -2357,7 +2580,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.94004</v>
+        <v>1.11003</v>
       </c>
     </row>
     <row r="11">
@@ -2396,7 +2619,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="19" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2422,7 +2645,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
@@ -2461,12 +2684,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2475,18 +2698,18 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>1.94004</v>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>1.11003</v>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>INJ=DB / ABS=ACTIVE</t>
         </is>
@@ -2499,18 +2722,18 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="19" t="n">
         <v>2.86276</v>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="E23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2523,18 +2746,18 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19" t="n">
         <v>2.3</v>
       </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="E24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2550,15 +2773,15 @@
         <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="19" t="n">
         <v>2.78796</v>
       </c>
-      <c r="E25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="E25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>
@@ -2567,4 +2790,250 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Bus ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>V (pu)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>V_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>V_max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.01909</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.00198</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9848170000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9628409999999999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.0038</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.00397</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.992563</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.01387</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.02689</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.01646</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,9 +49,6 @@
       <sz val="12"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -61,7 +58,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,12 +91,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
@@ -117,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,8 +116,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,10 +131,8 @@
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -703,8 +691,8 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -723,7 +711,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>solved</t>
+          <t>infeasible</t>
         </is>
       </c>
     </row>
@@ -734,7 +722,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1760.45</v>
+        <v>1760.450885</v>
       </c>
     </row>
     <row r="5">
@@ -754,7 +742,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.0972813272805</v>
+        <v>28.0972813512282</v>
       </c>
     </row>
     <row r="7">
@@ -800,102 +788,111 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Net Grid Q Losses (MVAr)</t>
+          <t>Net Reactive Line Losses (MVAr)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>-170.5313999999999</v>
+        <v>170.5313999999998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Avg Injection Price (€/MVAr)</t>
+          <t>Total Payment (€)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.627104269204994</v>
+        <v>1760.450885</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Avg Absorption Price (€/MVAr)</t>
+          <t>Pure Procurement Cost (€)</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.11003</v>
+        <v>1760.448636</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Generators Injecting</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
+          <t>Tikhonov Regularisation Cost (€)</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.00224903</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Generators Absorbing</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
+          <t>Avg Injection Price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2.627104269204994</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Avg Absorption Price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1.11003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Generators Injecting</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Generators Absorbing</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Generators Idle</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Consistency Checks</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Dual Price Consistency</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Gen 0 ABS stationarity FAIL: lam=1.1100, expected=-0.0000, residual=1.1100e+00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Gen 1 INJ stationarity FAIL: lam=2.8628, expected=0.0000, residual=2.8628e+00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>Gen 2 INJ stationarity FAIL: lam=2.3000, expected=0.0000, residual=2.3000e+00</t>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>INVALID (solver did not converge)</t>
         </is>
       </c>
     </row>
@@ -929,240 +926,240 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>λ_inj (€/MVAr)</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>λ_abs (€/MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Q_inj (MVAr)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Q_abs (MVAr)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Q_net (MVAr)</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>revenue (€)</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>cost (€)</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>profit (€)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>G0.0</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
+        <v>0.000378228</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <v>1.11003</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1.49607e-16</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>25.0106</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>-25.0106</v>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>ABSORPTION</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>27.762516318</v>
+      </c>
+      <c r="K2" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>1.11003</v>
-      </c>
-      <c r="F2" s="11" t="n">
+      <c r="L2" s="11" t="n">
+        <v>27.762516318</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>G1.0</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2.86276</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>0.000378304</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>212.552</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>1.21901e-22</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>212.552</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>608.48536352</v>
+      </c>
+      <c r="K3" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="11" t="n">
-        <v>25.0106</v>
-      </c>
-      <c r="H2" s="11" t="n">
-        <v>-25.0106</v>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>ABSORPTION</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>27.762516318</v>
-      </c>
-      <c r="K2" s="12" t="n">
+      <c r="L3" s="15" t="n">
+        <v>608.48536352</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>G2.0</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>0.000378297</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="G4" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="12" t="n">
-        <v>27.762516318</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>G1.0</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>2.86276</v>
-      </c>
-      <c r="E3" s="14" t="n">
+      <c r="H4" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>575</v>
+      </c>
+      <c r="K4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="15" t="n">
-        <v>212.552</v>
-      </c>
-      <c r="G3" s="15" t="n">
+      <c r="L4" s="15" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>G3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>2.78796</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.000378307</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="G5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="15" t="n">
-        <v>212.552</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="H5" s="14" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="16" t="n">
-        <v>608.48536352</v>
-      </c>
-      <c r="K3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="16" t="n">
-        <v>608.48536352</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>G2.0</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>575</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>G3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>2.78796</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>196.99</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>196.99</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="n">
+      <c r="J5" s="15" t="n">
         <v>549.2002404</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="15" t="n">
         <v>471.5901202</v>
       </c>
-      <c r="L5" s="16" t="n">
+      <c r="L5" s="15" t="n">
         <v>77.61012019999998</v>
       </c>
     </row>
@@ -1191,414 +1188,414 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>V_min</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>V_pu</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>V_max</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>θ (deg)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="13" t="n">
         <v>1.01909</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="16" t="n">
         <v>2.31982</v>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="13" t="n">
         <v>1.00198</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="16" t="n">
         <v>3.92947</v>
       </c>
-      <c r="G3" s="13" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="13" t="n">
         <v>0.9848170000000001</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="16" t="n">
         <v>-28.7024</v>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="16" t="n">
         <v>-33.8361</v>
       </c>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.9628409999999999</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="16" t="n">
         <v>-23.3898</v>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="13" t="n">
         <v>1.0038</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="16" t="n">
         <v>-26.4708</v>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="13" t="n">
         <v>1.00397</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="16" t="n">
         <v>-26.4581</v>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="13" t="n">
         <v>1.03</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="13" t="n">
         <v>0.992563</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="16" t="n">
         <v>-26.1255</v>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="13" t="n">
         <v>1.01387</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="16" t="n">
         <v>5.92667</v>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="13" t="n">
         <v>1.02689</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <v>7.55141</v>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="13" t="n">
         <v>1.01646</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <v>-27.214</v>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="13" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="13" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="16" t="n">
         <v>-22.2148</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1631,565 +1628,565 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>from_bus</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>to_bus</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>P_flow (MW)</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Q_flow (MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>|S_flow| (MVA)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>S_max (MVA)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>loading (%)</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="14" t="n">
         <v>30.5008</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="14" t="n">
         <v>-26.6978</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="14" t="n">
         <v>40.53481621371929</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="14" t="n">
         <v>434.3999628528669</v>
       </c>
-      <c r="H2" s="18" t="n">
+      <c r="H2" s="17" t="n">
         <v>0.0933122</v>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="14" t="n">
         <v>-203.673</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="14" t="n">
         <v>-24.1611</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="14" t="n">
         <v>205.1010718699686</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="14" t="n">
         <v>434.4008791117355</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="17" t="n">
         <v>0.472147</v>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="14" t="n">
         <v>-184.286</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="14" t="n">
         <v>-29.2815</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="14" t="n">
         <v>186.5977921580264</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="14" t="n">
         <v>434.4009390202498</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="17" t="n">
         <v>0.429552</v>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="14" t="n">
         <v>-213.058</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="14" t="n">
         <v>-57.5675</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="14" t="n">
         <v>220.6982746200115</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="14" t="n">
         <v>868.7984923650299</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="17" t="n">
         <v>0.254027</v>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>65.2741</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>-11.9104</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>66.35183312441337</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="14" t="n">
         <v>434.39894938206</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="17" t="n">
         <v>0.152744</v>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>51.0557</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>9.150499999999999</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>51.86922163229366</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="14" t="n">
         <v>434.4010387616299</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="17" t="n">
         <v>0.119404</v>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="14" t="n">
         <v>-354.926</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>-73.0012</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>362.3556825516056</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="14" t="n">
         <v>868.8001288772446</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.417076</v>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="14" t="n">
         <v>299.984</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="14" t="n">
         <v>166.525</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="14" t="n">
         <v>343.1049050669488</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="14" t="n">
         <v>434.3996357057834</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="17" t="n">
         <v>0.789837</v>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>1.0-8.0</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>-326.828</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>78.8883</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>336.2140768333325</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>1000.000228525084</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.336214</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>8.0-1.0</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>326.828</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>-93.038</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>339.8126116376495</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>999.9988571292137</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0.339813</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>3.0-9.0</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>338.058</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>51.0741</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>341.8943916691381</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>1000.001145586463</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>0.341894</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>9.0-3.0</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>-338.058</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>-66.7422</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>344.5834189638845</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>1000.001215857673</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0.344583</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="14" t="n">
         <v>-56.7067</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="14" t="n">
         <v>503.2053753934769</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="14" t="n">
         <v>1000.000746005061</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="17" t="n">
         <v>0.503205</v>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="14" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>176.162</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>530.1255042383831</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="14" t="n">
         <v>999.9990648230479</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="17" t="n">
         <v>0.530126</v>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="14" t="n">
         <v>237.103</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="14" t="n">
         <v>310.1899943728037</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="14" t="n">
         <v>999.9999818588727</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="17" t="n">
         <v>0.31019</v>
       </c>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="14" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="14" t="n">
         <v>166.614</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="14" t="n">
         <v>343.1620972601724</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="14" t="n">
         <v>499.9994131937091</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="17" t="n">
         <v>0.686325</v>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2214,10 +2211,10 @@
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
@@ -2226,67 +2223,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>μ_qp_ub</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>μ_qp_lb</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>μ_qn_ub</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>μ_qn_lb</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>stat_inj_residual</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>stat_abs_residual</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>compl_qp_ub_violation</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>compl_qp_lb_violation</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>compl_qn_ub_violation</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>compl_qn_lb_violation</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>exclusivity_violation</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>overall_status</t>
         </is>
@@ -2298,38 +2295,38 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n">
-        <v>3.38588e-16</v>
-      </c>
-      <c r="C2" s="19" t="n">
-        <v>0.699613</v>
-      </c>
-      <c r="D2" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="19" t="n">
-        <v>2.22045e-16</v>
-      </c>
-      <c r="F2" s="20" t="n">
-        <v>0.6996129999999997</v>
-      </c>
-      <c r="G2" s="20" t="n">
-        <v>1.11003</v>
-      </c>
-      <c r="H2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="14" t="n">
-        <v>5.553478677e-15</v>
-      </c>
-      <c r="L2" s="14" t="n">
-        <v>0</v>
+      <c r="B2" s="18" t="n">
+        <v>1.6683e-14</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <v>0.699622</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>2.67662e-14</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>3.8775e-22</v>
+      </c>
+      <c r="F2" s="19" t="n">
+        <v>0.7000002279999833</v>
+      </c>
+      <c r="G2" s="19" t="n">
+        <v>1.110029999999973</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>2.495893581e-30</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>1.04668348554e-16</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>6.6943872172e-13</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>9.69786015e-21</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>3.7417608342e-15</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -2343,38 +2340,38 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
-        <v>1.01095e-16</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>4.5265e-22</v>
-      </c>
-      <c r="D3" s="19" t="n">
+      <c r="B3" s="18" t="n">
+        <v>1.77784e-14</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>5.12453e-22</v>
+      </c>
+      <c r="D3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="19" t="n">
-        <v>2.69961</v>
-      </c>
-      <c r="F3" s="20" t="n">
-        <v>2.86276</v>
-      </c>
-      <c r="G3" s="20" t="n">
-        <v>2.69961</v>
-      </c>
-      <c r="H3" s="14" t="n">
-        <v>2.148794444e-14</v>
-      </c>
-      <c r="I3" s="14" t="n">
-        <v>9.621166279999999e-20</v>
-      </c>
-      <c r="J3" s="14" t="n">
+      <c r="E3" s="18" t="n">
+        <v>2.69962</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>2.862759999999982</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>2.699998304</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>3.7788344768e-12</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>1.08922910056e-19</v>
+      </c>
+      <c r="J3" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="14" t="n">
-        <v>0</v>
+      <c r="K3" s="13" t="n">
+        <v>3.2908637762e-22</v>
+      </c>
+      <c r="L3" s="13" t="n">
+        <v>2.5910301352e-20</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -2388,37 +2385,37 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>1.74705e-08</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>2.96811e-26</v>
-      </c>
-      <c r="D4" s="19" t="n">
+      <c r="B4" s="18" t="n">
+        <v>1.74706e-09</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>4.93731e-26</v>
+      </c>
+      <c r="D4" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="19" t="n">
-        <v>2.09961</v>
-      </c>
-      <c r="F4" s="20" t="n">
-        <v>2.2999999825295</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>2.09961</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>4.367625e-06</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>7.420275e-24</v>
-      </c>
-      <c r="J4" s="14" t="n">
+      <c r="E4" s="18" t="n">
+        <v>2.09962</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>2.29999999825294</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>2.099998297</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>4.36765e-07</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>1.2343275e-23</v>
+      </c>
+      <c r="J4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="K4" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="L4" s="13" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -2433,42 +2430,42 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>7.64796e-17</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>1.02754e-21</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>6.13047e-17</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>2.99961</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>7.647857245999999e-17</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>0.0003899999999998904</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>1.759795596000001e-15</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>2.024151046e-19</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>9.195705e-15</v>
-      </c>
-      <c r="K5" s="14" t="n">
+      <c r="B5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="C5" s="18" t="n">
+        <v>1.06914e-21</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>1.23704e-14</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>2.99962</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>1.06914e-21</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>1.693000012181756e-06</v>
+      </c>
+      <c r="H5" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="22" t="inlineStr">
-        <is>
-          <t>WARN</t>
+      <c r="I5" s="13" t="n">
+        <v>2.106098886e-19</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>1.85556e-12</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -2492,7 +2489,7 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2546,11 +2543,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>net_grid_q_losses_mvar</t>
+          <t>net_reactive_line_losses_mvar</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>-170.5313999999999</v>
+        <v>170.5313999999998</v>
       </c>
     </row>
     <row r="8">
@@ -2560,189 +2557,161 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1760.45</v>
+        <v>1760.450885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>average_injection_price_eur_mvar</t>
+          <t>procurement_cost_eur</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>2.627104269204994</v>
+        <v>1760.448636</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>average_absorption_price_eur_mvar</t>
+          <t>tikhonov_eur</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.11003</v>
+        <v>0.00224903</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>num_generators_injecting</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
+          <t>average_injection_price_eur_mvar</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>2.627104269204994</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>num_generators_absorbing</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
+          <t>average_absorption_price_eur_mvar</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1.11003</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>num_generators_idle</t>
+          <t>num_generators_injecting</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>max_voltage_deviation_pu</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>0.05000000000000004</v>
+          <t>num_generators_absorbing</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>num_generators_idle</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>max_voltage_deviation_pu</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>0.05000000000000004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>most_loaded_branch</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>6.0-&gt;7.0 (79.0%)</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Producer Deadbands</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>gen_id</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>injection_deadband_price (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>absorption_deadband_price (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>actual_lam_inj (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>actual_lam_abs (€/MVAr)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>in_deadband?</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>1.11003</v>
-      </c>
-      <c r="F22" s="24" t="inlineStr">
-        <is>
-          <t>INJ=DB / ABS=ACTIVE</t>
+          <t>gen_id</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>injection_deadband_price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>absorption_deadband_price (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>actual_lam_inj (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>actual_lam_abs (€/MVAr)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>in_deadband?</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>2.86276</v>
-      </c>
-      <c r="E23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="24" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
-        </is>
-      </c>
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
@@ -2751,37 +2720,85 @@
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="24" t="inlineStr">
-        <is>
-          <t>INJ=ACTIVE / ABS=DB</t>
+      <c r="D24" s="18" t="n">
+        <v>0.000378228</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1.11003</v>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2.86276</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>0.000378304</v>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>0.000378297</v>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>INJ=ACTIVE / ABS=ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D27" s="18" t="n">
         <v>2.78796</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="E27" s="18" t="n">
+        <v>0.000378307</v>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="0.000000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,9 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
@@ -108,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,7 +119,8 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,7 +135,7 @@
     <xf numFmtId="10" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -688,11 +692,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infeasible</t>
+          <t>solved</t>
         </is>
       </c>
     </row>
@@ -722,7 +726,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1760.450885</v>
+        <v>1760.450807</v>
       </c>
     </row>
     <row r="5">
@@ -742,7 +746,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.0972813512282</v>
+        <v>28.0973893393501</v>
       </c>
     </row>
     <row r="7">
@@ -802,7 +806,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1760.450885</v>
+        <v>1760.450807</v>
       </c>
     </row>
     <row r="13">
@@ -812,7 +816,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1760.448636</v>
+        <v>1760.446536</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +826,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.00224903</v>
+        <v>0.0042713</v>
       </c>
     </row>
     <row r="15">
@@ -892,7 +896,28 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>INVALID (solver did not converge)</t>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Gen 0 ABS stationarity FAIL: lam=1.1100 €/MVAr, expected=0.0000 €/MVAr, residual=1.1100e+00 €/MVAr</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Gen 1 INJ stationarity FAIL: lam=2.8628 €/MVAr, expected=0.0000 €/MVAr, residual=2.8628e+00 €/MVAr</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Gen 2 INJ stationarity FAIL: lam=2.3000 €/MVAr, expected=0.0000 €/MVAr, residual=2.3000e+00 €/MVAr</t>
         </is>
       </c>
     </row>
@@ -917,7 +942,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -926,240 +951,240 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>λ_inj (€/MVAr)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>λ_abs (€/MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Q_inj (MVAr)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Q_abs (MVAr)</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Q_net (MVAr)</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>revenue (€)</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>cost (€)</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>profit (€)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>G0.0</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
+      <c r="C2" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>0.000378228</v>
-      </c>
-      <c r="E2" s="9" t="n">
+      <c r="D2" s="10" t="n">
+        <v>0.680264</v>
+      </c>
+      <c r="E2" s="10" t="n">
         <v>1.11003</v>
       </c>
-      <c r="F2" s="10" t="n">
-        <v>1.49607e-16</v>
-      </c>
-      <c r="G2" s="10" t="n">
+      <c r="F2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>25.0106</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="11" t="n">
         <v>-25.0106</v>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>ABSORPTION</t>
         </is>
       </c>
-      <c r="J2" s="11" t="n">
+      <c r="J2" s="12" t="n">
         <v>27.762516318</v>
       </c>
-      <c r="K2" s="11" t="n">
+      <c r="K2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="11" t="n">
+      <c r="L2" s="12" t="n">
         <v>27.762516318</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>G1.0</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="14" t="n">
         <v>2.86276</v>
       </c>
-      <c r="E3" s="13" t="n">
-        <v>0.000378304</v>
-      </c>
-      <c r="F3" s="14" t="n">
+      <c r="E3" s="14" t="n">
+        <v>2.63918</v>
+      </c>
+      <c r="F3" s="15" t="n">
         <v>212.552</v>
       </c>
-      <c r="G3" s="14" t="n">
-        <v>1.21901e-22</v>
-      </c>
-      <c r="H3" s="14" t="n">
+      <c r="G3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="15" t="n">
         <v>212.552</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J3" s="15" t="n">
+      <c r="J3" s="16" t="n">
         <v>608.48536352</v>
       </c>
-      <c r="K3" s="15" t="n">
+      <c r="K3" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="15" t="n">
+      <c r="L3" s="16" t="n">
         <v>608.48536352</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>G2.0</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="14" t="n">
         <v>2.3</v>
       </c>
-      <c r="E4" s="13" t="n">
-        <v>0.000378297</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="E4" s="14" t="n">
+        <v>2.05024</v>
+      </c>
+      <c r="F4" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="15" t="n">
+        <v>1.70099e-20</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>INJECTION</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>575</v>
+      </c>
+      <c r="K4" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="L4" s="16" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>G3.0</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>2.78796</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>2.93108</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>8.900549999999999e-20</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>196.99</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>INJECTION</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>575</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="15" t="n">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>G3.0</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>2.78796</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0.000378307</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>196.99</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>196.99</v>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>INJECTION</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="n">
+      <c r="J5" s="16" t="n">
         <v>549.2002404</v>
       </c>
-      <c r="K5" s="15" t="n">
+      <c r="K5" s="16" t="n">
         <v>471.5901202</v>
       </c>
-      <c r="L5" s="15" t="n">
+      <c r="L5" s="16" t="n">
         <v>77.61012019999998</v>
       </c>
     </row>
@@ -1188,414 +1213,414 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>bus_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>V_min</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>V_pu</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>V_max</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>θ (deg)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="14" t="n">
         <v>1.01909</v>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="E2" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>2.31982</v>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="14" t="n">
         <v>1.00198</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>3.92947</v>
       </c>
-      <c r="G3" s="12" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="14" t="n">
         <v>0.9848170000000001</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>-28.7024</v>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>-33.8361</v>
       </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>0.9628409999999999</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="F6" s="17" t="n">
         <v>-23.3898</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>1.0038</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>-26.4708</v>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>1.00397</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="17" t="n">
         <v>-26.4581</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>1.03</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>0.992563</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>-26.1255</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>1.01387</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>5.92667</v>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>1.02689</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>7.55141</v>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>1.01646</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>-27.214</v>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="14" t="n">
         <v>0.95</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>1.05</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>-22.2148</v>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1628,565 +1653,565 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>from_bus</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>to_bus</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>P_flow (MW)</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Q_flow (MVAr)</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>|S_flow| (MVA)</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>S_max (MVA)</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>loading (%)</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>1.0-2.0</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="15" t="n">
         <v>30.5008</v>
       </c>
-      <c r="E2" s="14" t="n">
-        <v>-26.6978</v>
-      </c>
-      <c r="F2" s="14" t="n">
-        <v>40.53481621371929</v>
-      </c>
-      <c r="G2" s="14" t="n">
-        <v>434.3999628528669</v>
-      </c>
-      <c r="H2" s="17" t="n">
-        <v>0.0933122</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="E2" s="15" t="n">
+        <v>-26.6973</v>
+      </c>
+      <c r="F2" s="15" t="n">
+        <v>40.53448689609873</v>
+      </c>
+      <c r="G2" s="15" t="n">
+        <v>434.4001579238843</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>0.09331139999999999</v>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>1.0-6.0</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="15" t="n">
         <v>-203.673</v>
       </c>
-      <c r="E3" s="14" t="n">
-        <v>-24.1611</v>
-      </c>
-      <c r="F3" s="14" t="n">
-        <v>205.1010718699686</v>
-      </c>
-      <c r="G3" s="14" t="n">
-        <v>434.4008791117355</v>
-      </c>
-      <c r="H3" s="17" t="n">
+      <c r="E3" s="15" t="n">
+        <v>-24.1612</v>
+      </c>
+      <c r="F3" s="15" t="n">
+        <v>205.101083650087</v>
+      </c>
+      <c r="G3" s="15" t="n">
+        <v>434.4009040618432</v>
+      </c>
+      <c r="H3" s="18" t="n">
         <v>0.472147</v>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>2.0-5.0</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>-184.286</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>-29.2815</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="15" t="n">
         <v>186.5977921580264</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="15" t="n">
         <v>434.4009390202498</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>0.429552</v>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>3.0-4.0</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>-213.058</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>-57.5675</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="15" t="n">
         <v>220.6982746200115</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n">
         <v>868.7984923650299</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>0.254027</v>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>4.0-5.0</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>65.2741</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>-11.9104</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>66.35183312441337</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>434.39894938206</v>
-      </c>
-      <c r="H6" s="17" t="n">
+      <c r="D6" s="15" t="n">
+        <v>65.27419999999999</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-11.9103</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>66.35191354987435</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>434.3994759196718</v>
+      </c>
+      <c r="H6" s="18" t="n">
         <v>0.152744</v>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>4.0-6.0</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>51.0557</v>
       </c>
-      <c r="E7" s="14" t="n">
-        <v>9.150499999999999</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>51.86922163229366</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>434.4010387616299</v>
-      </c>
-      <c r="H7" s="17" t="n">
+      <c r="E7" s="15" t="n">
+        <v>9.150449999999999</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>51.86921281157542</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>434.4009648887426</v>
+      </c>
+      <c r="H7" s="18" t="n">
         <v>0.119404</v>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>8.0-9.0</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>-354.926</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>-73.0012</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>362.3556825516056</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n">
         <v>868.8001288772446</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <v>0.417076</v>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>6.0-7.0</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>299.984</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>166.525</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>343.1049050669488</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n">
         <v>434.3996357057834</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>0.789837</v>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>8.0-1.0</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>326.828</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>-93.038</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>339.8126116376495</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n">
         <v>999.9988571292137</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>0.339813</v>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>9.0-3.0</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>-338.058</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>-66.7422</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>344.5834189638845</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n">
         <v>1000.001215857673</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <v>0.344583</v>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>1.0-10.0</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>-56.7067</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>503.2053753934769</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>1000.000746005061</v>
-      </c>
-      <c r="H12" s="17" t="n">
+      <c r="E12" s="15" t="n">
+        <v>-56.7071</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>503.2054204700204</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>1000.000835583948</v>
+      </c>
+      <c r="H12" s="18" t="n">
         <v>0.503205</v>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>2.0-11.0</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>176.162</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>530.1255042383831</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>999.9990648230479</v>
-      </c>
-      <c r="H13" s="17" t="n">
+      <c r="E13" s="15" t="n">
+        <v>176.163</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>530.125836541665</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>999.9996916613503</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <v>0.530126</v>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>3.0-12.0</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="15" t="n">
         <v>200</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <v>237.103</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="15" t="n">
         <v>310.1899943728037</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="15" t="n">
         <v>999.9999818588727</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <v>0.31019</v>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>7.0-13.0</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <v>166.614</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <v>343.1620972601724</v>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>499.9994131937091</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>0.686325</v>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="G15" s="15" t="n">
+        <v>500.000141711746</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>0.686324</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2209,9 +2234,9 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
@@ -2223,67 +2248,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>gen_id</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>μ_qp_ub</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>μ_qp_lb</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>μ_qn_ub</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>μ_qn_lb</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>stat_inj_residual</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>stat_abs_residual</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>compl_qp_ub_violation</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>compl_qp_lb_violation</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>compl_qn_ub_violation</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>compl_qn_lb_violation</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>exclusivity_violation</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>overall_status</t>
         </is>
@@ -2295,38 +2320,38 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
-        <v>1.6683e-14</v>
-      </c>
-      <c r="C2" s="18" t="n">
-        <v>0.699622</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>2.67662e-14</v>
-      </c>
-      <c r="E2" s="18" t="n">
-        <v>3.8775e-22</v>
-      </c>
-      <c r="F2" s="19" t="n">
-        <v>0.7000002279999833</v>
-      </c>
-      <c r="G2" s="19" t="n">
-        <v>1.110029999999973</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>2.495893581e-30</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>1.04668348554e-16</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>6.6943872172e-13</v>
-      </c>
-      <c r="K2" s="13" t="n">
-        <v>9.69786015e-21</v>
-      </c>
-      <c r="L2" s="13" t="n">
-        <v>3.7417608342e-15</v>
+      <c r="B2" s="19" t="n">
+        <v>1.88185e-14</v>
+      </c>
+      <c r="C2" s="19" t="n">
+        <v>0.0197357</v>
+      </c>
+      <c r="D2" s="19" t="n">
+        <v>1.51972e-14</v>
+      </c>
+      <c r="E2" s="19" t="n">
+        <v>2.21588e-23</v>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>0.6999996999999811</v>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>1.110029999999985</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>3.8009109032e-13</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>5.542048832800001e-22</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -2340,38 +2365,38 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n">
-        <v>1.77784e-14</v>
-      </c>
-      <c r="C3" s="18" t="n">
-        <v>5.12453e-22</v>
-      </c>
-      <c r="D3" s="18" t="n">
+      <c r="B3" s="19" t="n">
+        <v>2.55932e-14</v>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>5.510130000000001e-40</v>
+      </c>
+      <c r="D3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>2.69962</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>2.862759999999982</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>2.699998304</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>3.7788344768e-12</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>1.08922910056e-19</v>
-      </c>
-      <c r="J3" s="13" t="n">
+      <c r="E3" s="19" t="n">
+        <v>0.0608245</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>2.862759999999974</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>2.7000045</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>5.4398858464e-12</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>1.17118915176e-37</v>
+      </c>
+      <c r="J3" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="13" t="n">
-        <v>3.2908637762e-22</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>2.5910301352e-20</v>
+      <c r="K3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -2385,38 +2410,38 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n">
-        <v>1.74706e-09</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>4.93731e-26</v>
-      </c>
-      <c r="D4" s="18" t="n">
+      <c r="B4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="18" t="n">
-        <v>2.09962</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>2.29999999825294</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>2.099998297</v>
-      </c>
-      <c r="H4" s="13" t="n">
-        <v>4.36765e-07</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>1.2343275e-23</v>
-      </c>
-      <c r="J4" s="13" t="n">
+      <c r="C4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="D4" s="19" t="n">
+        <v>5.447e-15</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>0.0497624</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>2.100002399999995</v>
+      </c>
+      <c r="H4" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="13" t="n">
+      <c r="I4" s="14" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>9.26529253e-35</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>8.4645344776e-22</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>4.252475e-18</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -2430,40 +2455,40 @@
           <t>3.0</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="19" t="n">
+        <v>2.49725e-15</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <v>1.06914e-21</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>1.23704e-14</v>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>2.99962</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>1.06914e-21</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>1.693000012181756e-06</v>
-      </c>
-      <c r="H5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="13" t="n">
-        <v>2.106098886e-19</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>1.85556e-12</v>
-      </c>
-      <c r="K5" s="13" t="n">
+      <c r="E5" s="19" t="n">
+        <v>0.0689155</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>2.49725e-15</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>4.499999999865723e-06</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>5.746172250000005e-14</v>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="J5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="K5" s="14" t="n">
+        <v>6.13385853525e-21</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>1.7533193445e-17</v>
+      </c>
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2557,7 +2582,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1760.450885</v>
+        <v>1760.450807</v>
       </c>
     </row>
     <row r="9">
@@ -2567,7 +2592,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1760.448636</v>
+        <v>1760.446536</v>
       </c>
     </row>
     <row r="10">
@@ -2577,7 +2602,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00224903</v>
+        <v>0.0042713</v>
       </c>
     </row>
     <row r="11">
@@ -2636,7 +2661,7 @@
           <t>max_voltage_deviation_pu</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="19" t="n">
         <v>0.05000000000000004</v>
       </c>
     </row>
@@ -2662,7 +2687,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>NOTE: lam_abs values are Tikhonov artefacts (≈δ_reg). True absorption market price is indeterminate when qn=0.</t>
         </is>
@@ -2701,12 +2726,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2720,13 +2745,13 @@
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="18" t="n">
-        <v>0.000378228</v>
-      </c>
-      <c r="E24" s="18" t="n">
+      <c r="D24" s="19" t="n">
+        <v>0.680264</v>
+      </c>
+      <c r="E24" s="19" t="n">
         <v>1.11003</v>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=ACTIVE</t>
         </is>
@@ -2744,13 +2769,13 @@
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="19" t="n">
         <v>2.86276</v>
       </c>
-      <c r="E25" s="18" t="n">
-        <v>0.000378304</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="E25" s="19" t="n">
+        <v>2.63918</v>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=ACTIVE</t>
         </is>
@@ -2768,13 +2793,13 @@
       <c r="C26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>2.3</v>
       </c>
-      <c r="E26" s="18" t="n">
-        <v>0.000378297</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="E26" s="19" t="n">
+        <v>2.05024</v>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=ACTIVE</t>
         </is>
@@ -2792,13 +2817,13 @@
       <c r="C27" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="19" t="n">
         <v>2.78796</v>
       </c>
-      <c r="E27" s="18" t="n">
-        <v>0.000378307</v>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="E27" s="19" t="n">
+        <v>2.93108</v>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>INJ=ACTIVE / ABS=DB</t>
         </is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -695,7 +695,7 @@
   <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="101" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1760.450807</v>
+        <v>1760.450779</v>
       </c>
     </row>
     <row r="5">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.0973893393501</v>
+        <v>27.6928544712733</v>
       </c>
     </row>
     <row r="7">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1760.450807</v>
+        <v>1760.450779</v>
       </c>
     </row>
     <row r="13">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1760.446536</v>
+        <v>1760.44864</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.0042713</v>
+        <v>0.00213877</v>
       </c>
     </row>
     <row r="15">
@@ -903,14 +903,14 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Gen 0 ABS stationarity FAIL: lam=1.1100 €/MVAr, expected=0.0000 €/MVAr, residual=1.1100e+00 €/MVAr</t>
+          <t>Gen 0 ABS stationarity FAIL: lam=1.1100 €/MVAr, expected=-0.0000 €/MVAr, residual=1.1100e+00 €/MVAr</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Gen 1 INJ stationarity FAIL: lam=2.8628 €/MVAr, expected=0.0000 €/MVAr, residual=2.8628e+00 €/MVAr</t>
+          <t>Gen 1 INJ stationarity FAIL: lam=2.8628 €/MVAr, expected=-0.0000 €/MVAr, residual=2.8628e+00 €/MVAr</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.680264</v>
+        <v>0.35995</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>1.11003</v>
@@ -1074,13 +1074,13 @@
         <v>2.86276</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2.63918</v>
+        <v>1.34818</v>
       </c>
       <c r="F3" s="15" t="n">
         <v>212.552</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>0</v>
+        <v>4.96787e-16</v>
       </c>
       <c r="H3" s="15" t="n">
         <v>212.552</v>
@@ -1118,13 +1118,13 @@
         <v>2.3</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2.05024</v>
+        <v>1.0489</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>250</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1.70099e-20</v>
+        <v>1.32653e-16</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>250</v>
@@ -1162,13 +1162,13 @@
         <v>2.78796</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>2.93108</v>
+        <v>1.49775</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>196.99</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>8.900549999999999e-20</v>
+        <v>0</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>196.99</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>30.5008</v>
+        <v>29.2293</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>-26.6973</v>
+        <v>-12.07</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>40.53448689609873</v>
+        <v>31.62335969643327</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>434.4001579238843</v>
+        <v>434.3999364875486</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>0.09331139999999999</v>
+        <v>0.0727978</v>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>-203.673</v>
+        <v>-202.72</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>-24.1612</v>
+        <v>-25.3552</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>205.101083650087</v>
+        <v>204.2994972265962</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>434.4009040618432</v>
+        <v>434.4006558054106</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0.472147</v>
+        <v>0.470302</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -1790,19 +1790,19 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>-184.286</v>
+        <v>-185.641</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-29.2815</v>
+        <v>-30.4811</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>186.5977921580264</v>
+        <v>188.1267613557678</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>434.4009390202498</v>
+        <v>434.4006570634161</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>0.429552</v>
+        <v>0.433072</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>-213.058</v>
+        <v>-212.423</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-57.5675</v>
+        <v>-56.9785</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>220.6982746200115</v>
+        <v>219.9319903771391</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>868.7984923650299</v>
+        <v>868.7984766720223</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>0.254027</v>
+        <v>0.253145</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>65.27419999999999</v>
+        <v>66.6609</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-11.9103</v>
+        <v>-9.91263</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>66.35191354987435</v>
+        <v>67.39388564496709</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>434.3994759196718</v>
+        <v>434.4012945879716</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.152744</v>
+        <v>0.155142</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -1901,19 +1901,19 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>51.0557</v>
+        <v>50.2723</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>9.150449999999999</v>
+        <v>7.39978</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>51.86921281157542</v>
+        <v>50.8139832264545</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>434.4009648887426</v>
+        <v>434.4003695358368</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0.119404</v>
+        <v>0.116975</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -1938,19 +1938,19 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>-354.926</v>
+        <v>-354.202</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-73.0012</v>
+        <v>-71.7804</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>362.3556825516056</v>
+        <v>361.4021065629806</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>868.8001288772446</v>
+        <v>868.7989214911825</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.417076</v>
+        <v>0.415979</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>299.984</v>
+        <v>299.981</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>166.525</v>
+        <v>162.813</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>343.1049050669488</v>
+        <v>341.3160900543659</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>434.3996357057834</v>
+        <v>434.3996900346891</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>0.789837</v>
+        <v>0.7857189999999999</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -2012,19 +2012,19 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>326.828</v>
+        <v>326.51</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-93.038</v>
+        <v>-94.25879999999999</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>339.8126116376495</v>
+        <v>339.8433484378354</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>999.9988571292137</v>
+        <v>1000.001025290606</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>0.339813</v>
+        <v>0.339843</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -2049,19 +2049,19 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>-338.058</v>
+        <v>-337.423</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-66.7422</v>
+        <v>-66.7174</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>344.5834189638845</v>
+        <v>343.9556546878682</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>1000.001215857673</v>
+        <v>999.9989960572518</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.344583</v>
+        <v>0.343956</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>500</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-56.7071</v>
+        <v>-71.34990000000001</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>503.2054204700204</v>
+        <v>505.0651524605613</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>1000.000835583948</v>
+        <v>1000.000301863248</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.503205</v>
+        <v>0.505065</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -2126,16 +2126,16 @@
         <v>500</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>176.163</v>
+        <v>190.847</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>530.125836541665</v>
+        <v>535.1846199294222</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>999.9996916613503</v>
+        <v>1000.001158348198</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.530126</v>
+        <v>0.535184</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -2163,16 +2163,16 @@
         <v>200</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>237.103</v>
+        <v>236.415</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>310.1899943728037</v>
+        <v>309.664418726143</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>999.9999818588727</v>
+        <v>1000.001352195098</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0.31019</v>
+        <v>0.309664</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -2200,16 +2200,16 @@
         <v>300</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>166.614</v>
+        <v>162.9</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>343.1620972601724</v>
+        <v>341.3742960446788</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>500.000141711746</v>
+        <v>500.0004336075371</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.686324</v>
+        <v>0.682748</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -2234,16 +2234,16 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -2321,22 +2321,22 @@
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>1.88185e-14</v>
+        <v>0</v>
       </c>
       <c r="C2" s="19" t="n">
-        <v>0.0197357</v>
+        <v>0.34005</v>
       </c>
       <c r="D2" s="19" t="n">
-        <v>1.51972e-14</v>
+        <v>0</v>
       </c>
       <c r="E2" s="19" t="n">
-        <v>2.21588e-23</v>
+        <v>2.03448e-15</v>
       </c>
       <c r="F2" s="20" t="n">
-        <v>0.6999996999999811</v>
+        <v>0.7</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>1.110029999999985</v>
+        <v>1.110030000000002</v>
       </c>
       <c r="H2" s="14" t="n">
         <v>0</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="14" t="n">
-        <v>3.8009109032e-13</v>
+        <v>0</v>
       </c>
       <c r="K2" s="14" t="n">
-        <v>5.542048832800001e-22</v>
+        <v>5.0883565488e-14</v>
       </c>
       <c r="L2" s="14" t="n">
         <v>0</v>
@@ -2366,37 +2366,37 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>2.55932e-14</v>
+        <v>2.01771e-15</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>5.510130000000001e-40</v>
+        <v>2.17245e-15</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>0.0608245</v>
+        <v>1.35182</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>2.862759999999974</v>
+        <v>2.86276</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>2.7000045</v>
+        <v>2.7</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>5.4398858464e-12</v>
+        <v>4.288682959199999e-13</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>1.17118915176e-37</v>
+        <v>4.617585924e-13</v>
       </c>
       <c r="J3" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="14" t="n">
-        <v>0</v>
+        <v>6.7156660234e-16</v>
       </c>
       <c r="L3" s="14" t="n">
-        <v>0</v>
+        <v>1.05593070424e-13</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -2411,37 +2411,37 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>0</v>
+        <v>4.939e-10</v>
       </c>
       <c r="C4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>5.447e-15</v>
+        <v>0</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>0.0497624</v>
+        <v>1.0511</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>2.3</v>
+        <v>2.2999999995061</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>2.100002399999995</v>
+        <v>2.1</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>0</v>
+        <v>1.23475e-07</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>9.26529253e-35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="14" t="n">
-        <v>8.4645344776e-22</v>
+        <v>1.394315683e-16</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>4.252475e-18</v>
+        <v>3.316325e-14</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -2456,37 +2456,37 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>2.49725e-15</v>
+        <v>0</v>
       </c>
       <c r="C5" s="19" t="n">
+        <v>2.01273e-15</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>3.31483e-15</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>1.50225</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>2.01273e-15</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>3.33066907387547e-15</v>
+      </c>
+      <c r="H5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="I5" s="14" t="n">
+        <v>3.964876827e-13</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>4.972244999999999e-13</v>
+      </c>
+      <c r="K5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.0689155</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>2.49725e-15</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>4.499999999865723e-06</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>5.746172250000005e-14</v>
-      </c>
-      <c r="I5" s="14" t="n">
+      <c r="L5" s="14" t="n">
         <v>0</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="14" t="n">
-        <v>6.13385853525e-21</v>
-      </c>
-      <c r="L5" s="14" t="n">
-        <v>1.7533193445e-17</v>
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1760.450807</v>
+        <v>1760.450779</v>
       </c>
     </row>
     <row r="9">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1760.446536</v>
+        <v>1760.44864</v>
       </c>
     </row>
     <row r="10">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.0042713</v>
+        <v>0.00213877</v>
       </c>
     </row>
     <row r="11">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.0-&gt;7.0 (79.0%)</t>
+          <t>6.0-&gt;7.0 (78.6%)</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0.680264</v>
+        <v>0.35995</v>
       </c>
       <c r="E24" s="19" t="n">
         <v>1.11003</v>
@@ -2773,7 +2773,7 @@
         <v>2.86276</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>2.63918</v>
+        <v>1.34818</v>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>2.3</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>2.05024</v>
+        <v>1.0489</v>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>2.78796</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>2.93108</v>
+        <v>1.49775</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -1015,12 +1015,12 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>G0.0</t>
+          <t>G0</t>
         </is>
       </c>
       <c r="C2" s="9" t="n">
@@ -1059,12 +1059,12 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>G1.0</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
@@ -1103,12 +1103,12 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>G2.0</t>
+          <t>G2</t>
         </is>
       </c>
       <c r="C4" s="13" t="n">
@@ -1147,12 +1147,12 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>G3.0</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
@@ -2317,7 +2317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" s="19" t="n">
@@ -2362,7 +2362,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="19" t="n">
@@ -2407,7 +2407,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" s="19" t="n">
@@ -2452,7 +2452,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">

--- a/output/stackelberg_results.xlsx
+++ b/output/stackelberg_results.xlsx
@@ -695,7 +695,7 @@
   <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="101" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1760.450779</v>
+        <v>126341.995528</v>
       </c>
     </row>
     <row r="5">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.6928544712733</v>
+        <v>27.0994860351541</v>
       </c>
     </row>
     <row r="7">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>659.542</v>
+        <v>680.702</v>
       </c>
     </row>
     <row r="8">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25.0106</v>
+        <v>59.9318</v>
       </c>
     </row>
     <row r="9">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>170.5313999999998</v>
+        <v>156.7701999999999</v>
       </c>
     </row>
     <row r="12">
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1760.450779</v>
+        <v>126341.995528</v>
       </c>
     </row>
     <row r="13">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1760.44864</v>
+        <v>126316.993818</v>
       </c>
     </row>
     <row r="14">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.00213877</v>
+        <v>25.0017106</v>
       </c>
     </row>
     <row r="15">
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2.627104269204994</v>
+        <v>185.463599549803</v>
       </c>
     </row>
     <row r="16">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.11003</v>
+        <v>1.19384</v>
       </c>
     </row>
     <row r="17">
@@ -903,21 +903,21 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Gen 0 ABS stationarity FAIL: lam=1.1100 €/MVAr, expected=-0.0000 €/MVAr, residual=1.1100e+00 €/MVAr</t>
+          <t>Gen 0 ABS stationarity FAIL: lam=1.1938 €/MVAr, expected=-0.0000 €/MVAr, residual=1.1938e+00 €/MVAr</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Gen 1 INJ stationarity FAIL: lam=2.8628 €/MVAr, expected=-0.0000 €/MVAr, residual=2.8628e+00 €/MVAr</t>
+          <t>Gen 1 INJ stationarity FAIL: lam=2.9891 €/MVAr, expected=0.0000 €/MVAr, residual=2.9891e+00 €/MVAr</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Gen 2 INJ stationarity FAIL: lam=2.3000 €/MVAr, expected=0.0000 €/MVAr, residual=2.3000e+00 €/MVAr</t>
+          <t>Gen 2 INJ stationarity FAIL: lam=500.0000 €/MVAr, expected=497.7000 €/MVAr, residual=2.3000e+00 €/MVAr</t>
         </is>
       </c>
     </row>
@@ -945,9 +945,9 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,19 +1027,19 @@
         <v>10</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>0.35995</v>
+        <v>0.69994</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>1.11003</v>
+        <v>1.19384</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>0</v>
+        <v>1.36786e-13</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>25.0106</v>
+        <v>59.9318</v>
       </c>
       <c r="H2" s="11" t="n">
-        <v>-25.0106</v>
+        <v>-59.9318</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="J2" s="12" t="n">
-        <v>27.762516318</v>
+        <v>71.54898011200011</v>
       </c>
       <c r="K2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>27.762516318</v>
+        <v>71.54898011200011</v>
       </c>
     </row>
     <row r="3">
@@ -1071,19 +1071,19 @@
         <v>11</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2.86276</v>
+        <v>2.98907</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1.34818</v>
+        <v>2.7</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>212.552</v>
+        <v>237.813</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>4.96787e-16</v>
+        <v>5.28323e-13</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>212.552</v>
+        <v>237.813</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="J3" s="16" t="n">
-        <v>608.48536352</v>
+        <v>710.8397039100014</v>
       </c>
       <c r="K3" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="16" t="n">
-        <v>608.48536352</v>
+        <v>710.8397039100014</v>
       </c>
     </row>
     <row r="4">
@@ -1115,16 +1115,16 @@
         <v>12</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2.3</v>
+        <v>500</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1.0489</v>
+        <v>2.1</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>250</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1.32653e-16</v>
+        <v>4.11526e-13</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>250</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>575</v>
+        <v>125000</v>
       </c>
       <c r="K4" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="16" t="n">
-        <v>575</v>
+        <v>125000</v>
       </c>
     </row>
     <row r="5">
@@ -1159,19 +1159,19 @@
         <v>13</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>2.78796</v>
+        <v>2.77156</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1.49775</v>
+        <v>3</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>196.99</v>
+        <v>192.889</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>6.48032e-13</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>196.99</v>
+        <v>192.889</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>549.2002404</v>
+        <v>534.603436840002</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>471.5901202</v>
+        <v>460.190332642002</v>
       </c>
       <c r="L5" s="16" t="n">
-        <v>77.61012019999998</v>
+        <v>74.41310419800004</v>
       </c>
     </row>
   </sheetData>
@@ -1264,13 +1264,13 @@
         <v>0.95</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>1.01909</v>
+        <v>1.01815</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F2" s="17" t="n">
-        <v>2.31982</v>
+        <v>2.31924</v>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         <v>0.95</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1.00198</v>
+        <v>1.02243</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F3" s="17" t="n">
-        <v>3.92947</v>
+        <v>3.60266</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -1322,13 +1322,13 @@
         <v>0.95</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>0.9848170000000001</v>
+        <v>0.99346</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F4" s="17" t="n">
-        <v>-28.7024</v>
+        <v>-28.3702</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -1351,13 +1351,13 @@
         <v>0.95</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.95</v>
+        <v>0.959574</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>-33.8361</v>
+        <v>-33.3868</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -1380,13 +1380,13 @@
         <v>0.95</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>0.9628409999999999</v>
+        <v>0.980648</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F6" s="17" t="n">
-        <v>-23.3898</v>
+        <v>-22.9426</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -1409,13 +1409,13 @@
         <v>0.95</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1.0038</v>
+        <v>1.00481</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>-26.4708</v>
+        <v>-26.2344</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         <v>0.95</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1.00397</v>
+        <v>1.00499</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F8" s="17" t="n">
-        <v>-26.4581</v>
+        <v>-26.2217</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         <v>0.95</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>0.992563</v>
+        <v>1.00085</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>-26.1255</v>
+        <v>-25.8453</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1525,13 +1525,13 @@
         <v>0.95</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1.01387</v>
+        <v>1.00838</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>5.92667</v>
+        <v>5.94911</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1554,13 +1554,13 @@
         <v>0.95</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1.02689</v>
+        <v>1.05</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F12" s="17" t="n">
-        <v>7.55141</v>
+        <v>7.07384</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1583,13 +1583,13 @@
         <v>0.95</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1.01646</v>
+        <v>1.02485</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1.05</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>-27.214</v>
+        <v>-26.9069</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>1.05</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>-22.2148</v>
+        <v>-21.9827</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>29.2293</v>
+        <v>28.4075</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>-12.07</v>
+        <v>0.325451</v>
       </c>
       <c r="F2" s="15" t="n">
-        <v>31.62335969643327</v>
+        <v>28.40936420625074</v>
       </c>
       <c r="G2" s="15" t="n">
-        <v>434.3999364875486</v>
+        <v>434.3992618602481</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>0.0727978</v>
+        <v>0.0653992</v>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
@@ -1753,19 +1753,19 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>-202.72</v>
+        <v>-201.963</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>-25.3552</v>
+        <v>-22.8083</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>204.2994972265962</v>
+        <v>203.2468251114639</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>434.4006558054106</v>
+        <v>434.4004007691389</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0.470302</v>
+        <v>0.467879</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -1790,19 +1790,19 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>-185.641</v>
+        <v>-186.487</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-30.4811</v>
+        <v>-29.5661</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>188.1267613557678</v>
+        <v>188.8161948515275</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>434.4006570634161</v>
+        <v>434.3987494887452</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>0.433072</v>
+        <v>0.434661</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1827,19 +1827,19 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>-212.423</v>
+        <v>-211.935</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-56.9785</v>
+        <v>-55.9877</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>219.9319903771391</v>
+        <v>219.2055354599651</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>868.7984766720223</v>
+        <v>868.7979242118397</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>0.253145</v>
+        <v>0.252309</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>66.6609</v>
+        <v>67.6353</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-9.91263</v>
+        <v>-9.21974</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>67.39388564496709</v>
+        <v>68.26080435914596</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>434.4012945879716</v>
+        <v>434.400363751263</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.155142</v>
+        <v>0.157138</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -1901,19 +1901,19 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>50.2723</v>
+        <v>49.7136</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>7.39978</v>
+        <v>6.39876</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>50.8139832264545</v>
+        <v>50.12370850702889</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>434.4003695358368</v>
+        <v>434.4002609244526</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0.116975</v>
+        <v>0.115386</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -1938,19 +1938,19 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>-354.202</v>
+        <v>-353.544</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-71.7804</v>
+        <v>-65.5313</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>361.4021065629806</v>
+        <v>359.5660039765856</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>868.7989214911825</v>
+        <v>868.8002222381348</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0.415979</v>
+        <v>0.413865</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -1975,19 +1975,19 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>299.981</v>
+        <v>299.984</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>162.813</v>
+        <v>162.802</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>341.3160900543659</v>
+        <v>341.3134797513863</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>434.3996900346891</v>
+        <v>434.3991321923579</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>0.7857189999999999</v>
+        <v>0.785714</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -2012,19 +2012,19 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>326.51</v>
+        <v>326.445</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-94.25879999999999</v>
+        <v>-100.508</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>339.8433484378354</v>
+        <v>341.5672643696992</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>1000.001025290606</v>
+        <v>1000.000773990752</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>0.339843</v>
+        <v>0.341567</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -2049,19 +2049,19 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>-337.423</v>
+        <v>-336.935</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-66.7174</v>
+        <v>-64.3181</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>343.9556546878682</v>
+        <v>343.0189677155041</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>999.9989960572518</v>
+        <v>999.9999058813187</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.343956</v>
+        <v>0.343019</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>500</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-71.34990000000001</v>
+        <v>-92.3531</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>505.0651524605613</v>
+        <v>508.4575646793054</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>1000.000301863248</v>
+        <v>999.9991438413899</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0.505065</v>
+        <v>0.508458</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -2126,16 +2126,16 @@
         <v>500</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>190.847</v>
+        <v>201.666</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>535.1846199294222</v>
+        <v>539.1374366114821</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>1000.001158348198</v>
+        <v>999.9989550198319</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.535184</v>
+        <v>0.539138</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -2163,16 +2163,16 @@
         <v>200</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>236.415</v>
+        <v>237.313</v>
       </c>
       <c r="F14" s="15" t="n">
-        <v>309.664418726143</v>
+        <v>310.3505436905178</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>1000.001352195098</v>
+        <v>999.9985296986889</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0.309664</v>
+        <v>0.310351</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -2200,16 +2200,16 @@
         <v>300</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>162.9</v>
+        <v>162.89</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>341.3742960446788</v>
+        <v>341.3695242695223</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>500.0004336075371</v>
+        <v>500.0000355472916</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0.682748</v>
+        <v>0.682739</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -2321,37 +2321,37 @@
         </is>
       </c>
       <c r="B2" s="19" t="n">
-        <v>0</v>
+        <v>5.88077e-14</v>
       </c>
       <c r="C2" s="19" t="n">
-        <v>0.34005</v>
+        <v>6.04075e-05</v>
       </c>
       <c r="D2" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="19" t="n">
-        <v>2.03448e-15</v>
+        <v>6.31369e-41</v>
       </c>
       <c r="F2" s="20" t="n">
-        <v>0.7</v>
+        <v>0.7000004074999412</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>1.110030000000002</v>
+        <v>1.19384</v>
       </c>
       <c r="H2" s="14" t="n">
-        <v>0</v>
+        <v>8.0440700522e-27</v>
       </c>
       <c r="I2" s="14" t="n">
-        <v>0</v>
+        <v>8.262900295e-18</v>
       </c>
       <c r="J2" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="14" t="n">
-        <v>5.0883565488e-14</v>
+        <v>3.78390806342e-39</v>
       </c>
       <c r="L2" s="14" t="n">
-        <v>0</v>
+        <v>8.1978311948e-12</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -2366,37 +2366,37 @@
         </is>
       </c>
       <c r="B3" s="19" t="n">
-        <v>2.01771e-15</v>
+        <v>2.25855e-17</v>
       </c>
       <c r="C3" s="19" t="n">
-        <v>2.17245e-15</v>
+        <v>0</v>
       </c>
       <c r="D3" s="19" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>1.35182</v>
+        <v>2.4835e-06</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>2.86276</v>
+        <v>2.98907</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>2.7</v>
+        <v>2.7000024835</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>4.288682959199999e-13</v>
+        <v>5.371125511499999e-15</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>4.617585924e-13</v>
+        <v>0</v>
       </c>
       <c r="J3" s="14" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="14" t="n">
-        <v>6.7156660234e-16</v>
+        <v>1.3120901705e-18</v>
       </c>
       <c r="L3" s="14" t="n">
-        <v>1.05593070424e-13</v>
+        <v>1.25642077599e-10</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -2411,37 +2411,37 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>4.939e-10</v>
+        <v>497.7</v>
       </c>
       <c r="C4" s="19" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>0</v>
+        <v>6.07885e-15</v>
       </c>
       <c r="E4" s="19" t="n">
-        <v>1.0511</v>
+        <v>2.9726e-06</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>2.2999999995061</v>
+        <v>2.300000000000011</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>1.23475e-07</v>
+        <v>2.100002972599994</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>124425</v>
       </c>
       <c r="I4" s="14" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>0</v>
+        <v>2.5016048251e-27</v>
       </c>
       <c r="K4" s="14" t="n">
-        <v>1.394315683e-16</v>
+        <v>1.2233021876e-18</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>3.316325e-14</v>
+        <v>1.028815e-10</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -2456,37 +2456,37 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
+        <v>4.84978e-15</v>
+      </c>
+      <c r="C5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="19" t="n">
-        <v>2.01273e-15</v>
-      </c>
       <c r="D5" s="19" t="n">
-        <v>3.31483e-15</v>
+        <v>0</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>1.50225</v>
+        <v>2.37615e-06</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2.01273e-15</v>
+        <v>3.999999995265242e-06</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3.33066907387547e-15</v>
+        <v>2.376149996003197e-06</v>
       </c>
       <c r="H5" s="14" t="n">
+        <v>1.314823855800001e-13</v>
+      </c>
+      <c r="I5" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="14" t="n">
-        <v>3.964876827e-13</v>
-      </c>
       <c r="J5" s="14" t="n">
-        <v>4.972244999999999e-13</v>
+        <v>0</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>0</v>
+        <v>1.5398212368e-18</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>0</v>
+        <v>1.24998244448e-10</v>
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>659.542</v>
+        <v>680.702</v>
       </c>
     </row>
     <row r="4">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>25.0106</v>
+        <v>59.9318</v>
       </c>
     </row>
     <row r="5">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>170.5313999999998</v>
+        <v>156.7701999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1760.450779</v>
+        <v>126341.995528</v>
       </c>
     </row>
     <row r="9">
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1760.44864</v>
+        <v>126316.993818</v>
       </c>
     </row>
     <row r="10">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00213877</v>
+        <v>25.0017106</v>
       </c>
     </row>
     <row r="11">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2.627104269204994</v>
+        <v>185.463599549803</v>
       </c>
     </row>
     <row r="12">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1.11003</v>
+        <v>1.19384</v>
       </c>
     </row>
     <row r="13">
@@ -2746,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>0.35995</v>
+        <v>0.69994</v>
       </c>
       <c r="E24" s="19" t="n">
-        <v>1.11003</v>
+        <v>1.19384</v>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>2.86276</v>
+        <v>2.98907</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>1.34818</v>
+        <v>2.7</v>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>2.3</v>
+        <v>500</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>1.0489</v>
+        <v>2.1</v>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
@@ -2818,10 +2818,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>2.78796</v>
+        <v>2.77156</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>1.49775</v>
+        <v>3</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.01909</v>
+        <v>1.01815</v>
       </c>
       <c r="C2" t="n">
         <v>0.95</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.00198</v>
+        <v>1.02243</v>
       </c>
       <c r="C3" t="n">
         <v>0.95</v>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9848170000000001</v>
+        <v>0.99346</v>
       </c>
       <c r="C4" t="n">
         <v>0.95</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.95</v>
+        <v>0.959574</v>
       </c>
       <c r="C5" t="n">
         <v>0.95</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9628409999999999</v>
+        <v>0.980648</v>
       </c>
       <c r="C6" t="n">
         <v>0.95</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.0038</v>
+        <v>1.00481</v>
       </c>
       <c r="C7" t="n">
         <v>0.95</v>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.00397</v>
+        <v>1.00499</v>
       </c>
       <c r="C8" t="n">
         <v>0.95</v>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.992563</v>
+        <v>1.00085</v>
       </c>
       <c r="C10" t="n">
         <v>0.95</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.01387</v>
+        <v>1.00838</v>
       </c>
       <c r="C11" t="n">
         <v>0.95</v>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.02689</v>
+        <v>1.05</v>
       </c>
       <c r="C12" t="n">
         <v>0.95</v>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.01646</v>
+        <v>1.02485</v>
       </c>
       <c r="C13" t="n">
         <v>0.95</v>
